--- a/test/standard_mapping/input-dpr部分.xlsx
+++ b/test/standard_mapping/input-dpr部分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Program\VScode\workspace\data-governance\test\standard_mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C532BE-3229-43AE-A93B-1D4B28062F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B503E9A0-C452-4553-B5FA-473E61B9E391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3330" uniqueCount="1314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="1325">
   <si>
     <t>上游信息</t>
   </si>
@@ -1822,9 +1822,6 @@
   </si>
   <si>
     <t>是否存在附件</t>
-  </si>
-  <si>
-    <t>是、否</t>
   </si>
   <si>
     <t>1. 代码枚举类字段的'是否枚举'必须为'是'，实际为'否'
@@ -2735,9 +2732,6 @@
     <t>分公司</t>
   </si>
   <si>
-    <t>an..(200)</t>
-  </si>
-  <si>
     <t>案件在发送邮件时所属的催收机构分公司</t>
   </si>
   <si>
@@ -2777,9 +2771,6 @@
     <t>电子律师函模板</t>
   </si>
   <si>
-    <t>an..(60)</t>
-  </si>
-  <si>
     <t>电子律师函模板内容</t>
   </si>
   <si>
@@ -2816,9 +2807,6 @@
     <t>记录人</t>
   </si>
   <si>
-    <t>记录人名称</t>
-  </si>
-  <si>
     <t>电子律师函提醒/查询短信行动流水系统或手工发起催收员号</t>
   </si>
   <si>
@@ -2840,9 +2828,6 @@
     <t>单人巡航模式</t>
   </si>
   <si>
-    <t>单人巡航模式/机器人模式</t>
-  </si>
-  <si>
     <t>一键外呼选择的模式 单人巡航模式/机器人模式</t>
   </si>
   <si>
@@ -2918,9 +2903,6 @@
     <t>电催特殊案件</t>
   </si>
   <si>
-    <t>电催特殊案件、直催问题质检</t>
-  </si>
-  <si>
     <t>分行特殊案件处理的类型</t>
   </si>
   <si>
@@ -3009,9 +2991,6 @@
   </si>
   <si>
     <t>成功</t>
-  </si>
-  <si>
-    <t>成功、失败</t>
   </si>
   <si>
     <t>分行邮寄单号导入文的上传结果</t>
@@ -4034,6 +4013,78 @@
   </si>
   <si>
     <t>anc..(200)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anc..(60)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anc..(100)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>an..(50)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01-单人巡航模式/02-机器人模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anc..(50)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标志类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anc..(200)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01电催特殊案件、02直催问题质检</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anc..(20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01成功、02失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anc..(30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>an..(20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1是0否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y是N否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1是、0否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01高、02中、03低、04空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4169,7 +4220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4239,6 +4290,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4246,11 +4304,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4583,41 +4640,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="25" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="25" t="s">
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" t="s">
@@ -4722,7 +4779,7 @@
         <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="V3" t="s">
         <v>37</v>
@@ -4751,7 +4808,7 @@
         <v>43</v>
       </c>
       <c r="R4" t="s">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="V4" t="s">
         <v>37</v>
@@ -4812,7 +4869,7 @@
         <v>51</v>
       </c>
       <c r="V6" t="s">
-        <v>1260</v>
+        <v>1253</v>
       </c>
       <c r="W6" t="s">
         <v>53</v>
@@ -4879,7 +4936,7 @@
         <v>53</v>
       </c>
       <c r="Y8" t="s">
-        <v>1261</v>
+        <v>1254</v>
       </c>
       <c r="AA8" t="s">
         <v>38</v>
@@ -5021,7 +5078,7 @@
         <v>53</v>
       </c>
       <c r="Y13" t="s">
-        <v>1262</v>
+        <v>1255</v>
       </c>
       <c r="AA13" t="s">
         <v>38</v>
@@ -5038,7 +5095,7 @@
         <v>80</v>
       </c>
       <c r="P14" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>81</v>
@@ -5067,7 +5124,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>1264</v>
+        <v>1257</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>84</v>
@@ -5096,7 +5153,7 @@
         <v>86</v>
       </c>
       <c r="P16" t="s">
-        <v>1265</v>
+        <v>1258</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>87</v>
@@ -5108,7 +5165,7 @@
         <v>37</v>
       </c>
       <c r="Y16" t="s">
-        <v>1266</v>
+        <v>1259</v>
       </c>
       <c r="AA16" t="s">
         <v>38</v>
@@ -5157,7 +5214,7 @@
         <v>94</v>
       </c>
       <c r="R18" t="s">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="V18" t="s">
         <v>37</v>
@@ -5180,13 +5237,13 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>1265</v>
+        <v>1258</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>96</v>
       </c>
       <c r="R19" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="V19" t="s">
         <v>37</v>
@@ -5455,10 +5512,10 @@
         <v>51</v>
       </c>
       <c r="V29" t="s">
+        <v>1253</v>
+      </c>
+      <c r="W29" t="s">
         <v>1260</v>
-      </c>
-      <c r="W29" t="s">
-        <v>1267</v>
       </c>
       <c r="Y29" t="s">
         <v>127</v>
@@ -5487,10 +5544,10 @@
         <v>51</v>
       </c>
       <c r="V30" t="s">
+        <v>1253</v>
+      </c>
+      <c r="W30" t="s">
         <v>1260</v>
-      </c>
-      <c r="W30" t="s">
-        <v>1267</v>
       </c>
       <c r="Y30" s="18" t="s">
         <v>130</v>
@@ -5624,7 +5681,7 @@
         <v>149</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>37</v>
@@ -5637,7 +5694,7 @@
         <v>54</v>
       </c>
       <c r="AC35" t="s">
-        <v>1268</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="36" spans="10:29" ht="30" customHeight="1">
@@ -5705,7 +5762,7 @@
         <v>159</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>1270</v>
+        <v>1263</v>
       </c>
       <c r="Q38" s="1" t="s">
         <v>160</v>
@@ -5735,7 +5792,7 @@
         <v>163</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
       <c r="Q39" s="1" t="s">
         <v>164</v>
@@ -5908,7 +5965,7 @@
         <v>184</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>37</v>
@@ -5921,7 +5978,7 @@
         <v>54</v>
       </c>
       <c r="AC45" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="46" spans="10:29" ht="30" customHeight="1">
@@ -5965,7 +6022,7 @@
         <v>184</v>
       </c>
       <c r="R47" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V47" s="24" t="s">
         <v>37</v>
@@ -5978,7 +6035,7 @@
         <v>54</v>
       </c>
       <c r="AC47" s="18" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="48" spans="10:29" s="18" customFormat="1" ht="30" customHeight="1">
@@ -5995,7 +6052,7 @@
         <v>184</v>
       </c>
       <c r="R48" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V48" s="24" t="s">
         <v>37</v>
@@ -6025,7 +6082,7 @@
         <v>184</v>
       </c>
       <c r="R49" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V49" s="24" t="s">
         <v>37</v>
@@ -6055,7 +6112,7 @@
         <v>184</v>
       </c>
       <c r="R50" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V50" s="24" t="s">
         <v>37</v>
@@ -6085,7 +6142,7 @@
         <v>184</v>
       </c>
       <c r="R51" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V51" s="24" t="s">
         <v>37</v>
@@ -6115,7 +6172,7 @@
         <v>205</v>
       </c>
       <c r="R52" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V52" s="24" t="s">
         <v>37</v>
@@ -6145,7 +6202,7 @@
         <v>205</v>
       </c>
       <c r="R53" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V53" s="24" t="s">
         <v>37</v>
@@ -6175,7 +6232,7 @@
         <v>205</v>
       </c>
       <c r="R54" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V54" s="24" t="s">
         <v>37</v>
@@ -6205,7 +6262,7 @@
         <v>205</v>
       </c>
       <c r="R55" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V55" s="24" t="s">
         <v>37</v>
@@ -6235,7 +6292,7 @@
         <v>205</v>
       </c>
       <c r="R56" s="24" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="V56" s="24" t="s">
         <v>37</v>
@@ -6259,7 +6316,7 @@
         <v>220</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
       <c r="Q57" s="1" t="s">
         <v>164</v>
@@ -6346,7 +6403,7 @@
         <v>227</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
       <c r="Q60" s="1" t="s">
         <v>160</v>
@@ -6403,7 +6460,7 @@
         <v>232</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
       <c r="Q62" s="1" t="s">
         <v>233</v>
@@ -6546,7 +6603,7 @@
         <v>248</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>1275</v>
+        <v>1268</v>
       </c>
       <c r="Q67" s="1" t="s">
         <v>249</v>
@@ -6765,7 +6822,7 @@
         <v>269</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="Q75" s="1" t="s">
         <v>270</v>
@@ -6801,7 +6858,7 @@
         <v>274</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="V76" s="1" t="s">
         <v>37</v>
@@ -6814,7 +6871,7 @@
         <v>54</v>
       </c>
       <c r="AC76" t="s">
-        <v>1277</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="77" spans="10:29" ht="30" customHeight="1">
@@ -6831,7 +6888,7 @@
         <v>56</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="V77" s="1" t="s">
         <v>37</v>
@@ -6844,7 +6901,7 @@
         <v>54</v>
       </c>
       <c r="AC77" t="s">
-        <v>1279</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="78" spans="10:29" ht="30" customHeight="1">
@@ -6861,7 +6918,7 @@
         <v>46</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="V78" s="1" t="s">
         <v>52</v>
@@ -6893,7 +6950,7 @@
         <v>46</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="V79" s="1" t="s">
         <v>52</v>
@@ -7195,7 +7252,7 @@
         <v>269</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="Q90" s="1" t="s">
         <v>270</v>
@@ -7290,7 +7347,7 @@
         <v>274</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="V93" s="1" t="s">
         <v>37</v>
@@ -7303,7 +7360,7 @@
         <v>54</v>
       </c>
       <c r="AC93" t="s">
-        <v>1282</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="94" spans="10:29" ht="30" customHeight="1">
@@ -7320,7 +7377,7 @@
         <v>46</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="V94" s="1" t="s">
         <v>52</v>
@@ -7855,7 +7912,7 @@
         <v>293</v>
       </c>
       <c r="R114" s="17" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="V114" s="17" t="s">
         <v>52</v>
@@ -7864,7 +7921,7 @@
         <v>294</v>
       </c>
       <c r="Y114" s="17" t="s">
-        <v>1284</v>
+        <v>1277</v>
       </c>
       <c r="AA114" s="18" t="s">
         <v>38</v>
@@ -8020,7 +8077,7 @@
         <v>293</v>
       </c>
       <c r="R120" s="2" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="V120" s="2" t="s">
         <v>52</v>
@@ -8385,7 +8442,7 @@
         <v>52</v>
       </c>
       <c r="W133" s="8" t="s">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="Y133" s="8" t="s">
         <v>417</v>
@@ -8493,7 +8550,7 @@
         <v>114</v>
       </c>
       <c r="Q137" s="8" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="R137" s="8" t="s">
         <v>116</v>
@@ -8541,7 +8598,7 @@
     </row>
     <row r="139" spans="10:29" ht="30" customHeight="1">
       <c r="J139" s="7" t="s">
-        <v>1287</v>
+        <v>1280</v>
       </c>
       <c r="O139" s="8" t="s">
         <v>436</v>
@@ -8639,7 +8696,7 @@
         <v>450</v>
       </c>
       <c r="P142" s="7" t="s">
-        <v>1288</v>
+        <v>1281</v>
       </c>
       <c r="Q142" s="8">
         <v>0</v>
@@ -8669,7 +8726,7 @@
         <v>453</v>
       </c>
       <c r="P143" s="7" t="s">
-        <v>1289</v>
+        <v>1282</v>
       </c>
       <c r="Q143" s="8" t="s">
         <v>454</v>
@@ -8758,7 +8815,7 @@
         <v>155</v>
       </c>
       <c r="Q146" s="8" t="s">
-        <v>1291</v>
+        <v>1284</v>
       </c>
       <c r="R146" s="8" t="s">
         <v>116</v>
@@ -8774,7 +8831,7 @@
         <v>54</v>
       </c>
       <c r="AC146" s="3" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="147" spans="10:29" ht="30" customHeight="1">
@@ -8897,7 +8954,7 @@
         <v>479</v>
       </c>
       <c r="P151" s="7" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
       <c r="Q151" s="8">
         <v>1.5283</v>
@@ -8927,7 +8984,7 @@
         <v>482</v>
       </c>
       <c r="P152" s="7" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
       <c r="Q152" s="8">
         <v>1.5283</v>
@@ -9127,7 +9184,7 @@
         <v>500</v>
       </c>
       <c r="P159" s="7" t="s">
-        <v>1289</v>
+        <v>1282</v>
       </c>
       <c r="Q159" s="8">
         <v>5.2200000000000003E-2</v>
@@ -9331,7 +9388,7 @@
         <v>52</v>
       </c>
       <c r="W166" s="8" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
       <c r="Y166" s="8" t="s">
         <v>521</v>
@@ -9417,7 +9474,7 @@
         <v>52</v>
       </c>
       <c r="W169" s="8" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="Y169" s="8" t="s">
         <v>530</v>
@@ -9464,7 +9521,7 @@
         <v>533</v>
       </c>
       <c r="P171" s="7" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="Q171" s="8" t="s">
         <v>534</v>
@@ -9911,7 +9968,7 @@
         <v>52</v>
       </c>
       <c r="W187" s="8" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
       <c r="Y187" s="8" t="s">
         <v>583</v>
@@ -9960,7 +10017,7 @@
         <v>588</v>
       </c>
       <c r="P189" s="7" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
       <c r="Q189" s="8">
         <v>1</v>
@@ -9999,7 +10056,7 @@
         <v>116</v>
       </c>
       <c r="V190" s="7" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="W190" s="8"/>
       <c r="Y190" s="8" t="s">
@@ -10032,7 +10089,7 @@
         <v>52</v>
       </c>
       <c r="W191" s="8" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
       <c r="Y191" s="8" t="s">
         <v>465</v>
@@ -10058,13 +10115,13 @@
         <v>596</v>
       </c>
       <c r="R192" s="8" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="V192" s="7" t="s">
-        <v>1299</v>
+        <v>1292</v>
       </c>
       <c r="W192" s="8" t="s">
-        <v>1300</v>
+        <v>1293</v>
       </c>
       <c r="Y192" s="8" t="s">
         <v>597</v>
@@ -10073,21 +10130,21 @@
         <v>38</v>
       </c>
       <c r="AB192" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="193" spans="10:29" ht="30" customHeight="1">
       <c r="J193" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="O193" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="O193" s="8" t="s">
+      <c r="P193" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="P193" s="7" t="s">
+      <c r="Q193" s="8" t="s">
         <v>602</v>
-      </c>
-      <c r="Q193" s="8" t="s">
-        <v>603</v>
       </c>
       <c r="R193" s="8" t="s">
         <v>36</v>
@@ -10097,7 +10154,7 @@
       </c>
       <c r="W193" s="8"/>
       <c r="Y193" s="8" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AA193" t="s">
         <v>54</v>
@@ -10105,16 +10162,16 @@
     </row>
     <row r="194" spans="10:29" ht="30" customHeight="1">
       <c r="J194" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O194" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="P194" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="P194" s="7" t="s">
+      <c r="Q194" s="8" t="s">
         <v>605</v>
-      </c>
-      <c r="Q194" s="8" t="s">
-        <v>606</v>
       </c>
       <c r="R194" s="8" t="s">
         <v>36</v>
@@ -10124,7 +10181,7 @@
       </c>
       <c r="W194" s="8"/>
       <c r="Y194" s="8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AA194" t="s">
         <v>54</v>
@@ -10132,16 +10189,16 @@
     </row>
     <row r="195" spans="10:29" ht="30" customHeight="1">
       <c r="J195" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O195" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="P195" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q195" s="8" t="s">
         <v>607</v>
-      </c>
-      <c r="P195" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="Q195" s="8" t="s">
-        <v>608</v>
       </c>
       <c r="R195" s="8" t="s">
         <v>36</v>
@@ -10151,7 +10208,7 @@
       </c>
       <c r="W195" s="8"/>
       <c r="Y195" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AA195" t="s">
         <v>38</v>
@@ -10162,16 +10219,16 @@
     </row>
     <row r="196" spans="10:29" ht="60" customHeight="1">
       <c r="J196" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="O196" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="O196" s="8" t="s">
+      <c r="P196" s="7" t="s">
         <v>610</v>
       </c>
-      <c r="P196" s="7" t="s">
+      <c r="Q196" s="8" t="s">
         <v>611</v>
-      </c>
-      <c r="Q196" s="8" t="s">
-        <v>612</v>
       </c>
       <c r="R196" s="8" t="s">
         <v>71</v>
@@ -10180,10 +10237,10 @@
         <v>52</v>
       </c>
       <c r="W196" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y196" s="8" t="s">
         <v>613</v>
-      </c>
-      <c r="Y196" s="8" t="s">
-        <v>614</v>
       </c>
       <c r="AA196" t="s">
         <v>54</v>
@@ -10191,16 +10248,16 @@
     </row>
     <row r="197" spans="10:29" ht="60" customHeight="1">
       <c r="J197" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="O197" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="O197" s="8" t="s">
+      <c r="P197" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q197" s="8" t="s">
         <v>616</v>
-      </c>
-      <c r="P197" s="7" t="s">
-        <v>611</v>
-      </c>
-      <c r="Q197" s="8" t="s">
-        <v>617</v>
       </c>
       <c r="R197" s="8" t="s">
         <v>71</v>
@@ -10209,30 +10266,30 @@
         <v>52</v>
       </c>
       <c r="W197" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="Y197" s="8" t="s">
         <v>618</v>
-      </c>
-      <c r="Y197" s="8" t="s">
-        <v>619</v>
       </c>
       <c r="AA197" t="s">
         <v>38</v>
       </c>
       <c r="AB197" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="198" spans="10:29" ht="15" customHeight="1">
       <c r="J198" s="8" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="O198" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="P198" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="P198" s="7" t="s">
+      <c r="Q198" s="8" t="s">
         <v>622</v>
-      </c>
-      <c r="Q198" s="8" t="s">
-        <v>623</v>
       </c>
       <c r="R198" s="8" t="s">
         <v>116</v>
@@ -10242,7 +10299,7 @@
       </c>
       <c r="W198" s="8"/>
       <c r="Y198" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AA198" t="s">
         <v>54</v>
@@ -10250,16 +10307,16 @@
     </row>
     <row r="199" spans="10:29" ht="15" customHeight="1">
       <c r="J199" s="8" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="O199" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="P199" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q199" s="8" t="s">
         <v>624</v>
-      </c>
-      <c r="P199" s="7" t="s">
-        <v>1276</v>
-      </c>
-      <c r="Q199" s="8" t="s">
-        <v>625</v>
       </c>
       <c r="R199" s="8" t="s">
         <v>116</v>
@@ -10269,27 +10326,27 @@
       </c>
       <c r="W199" s="8"/>
       <c r="Y199" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AA199" t="s">
         <v>38</v>
       </c>
       <c r="AB199" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="200" spans="10:29" ht="30" customHeight="1">
       <c r="J200" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="O200" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="O200" s="8" t="s">
+      <c r="P200" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q200" s="8" t="s">
         <v>628</v>
-      </c>
-      <c r="P200" s="7" t="s">
-        <v>611</v>
-      </c>
-      <c r="Q200" s="8" t="s">
-        <v>629</v>
       </c>
       <c r="R200" s="8" t="s">
         <v>51</v>
@@ -10298,10 +10355,10 @@
         <v>52</v>
       </c>
       <c r="W200" s="8" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Y200" s="8" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AA200" t="s">
         <v>54</v>
@@ -10309,16 +10366,16 @@
     </row>
     <row r="201" spans="10:29" ht="30" customHeight="1">
       <c r="J201" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="O201" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="P201" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q201" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R201" s="8" t="s">
         <v>51</v>
@@ -10327,10 +10384,10 @@
         <v>52</v>
       </c>
       <c r="W201" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="Y201" s="8" t="s">
         <v>630</v>
-      </c>
-      <c r="Y201" s="8" t="s">
-        <v>631</v>
       </c>
       <c r="AA201" t="s">
         <v>54</v>
@@ -10338,16 +10395,16 @@
     </row>
     <row r="202" spans="10:29" ht="30" customHeight="1">
       <c r="J202" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="O202" s="8" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="P202" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q202" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R202" s="8" t="s">
         <v>51</v>
@@ -10356,10 +10413,10 @@
         <v>52</v>
       </c>
       <c r="W202" s="8" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Y202" s="8" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AA202" t="s">
         <v>54</v>
@@ -10367,16 +10424,16 @@
     </row>
     <row r="203" spans="10:29" ht="30" customHeight="1">
       <c r="J203" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="O203" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="P203" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q203" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R203" s="8" t="s">
         <v>51</v>
@@ -10385,10 +10442,10 @@
         <v>52</v>
       </c>
       <c r="W203" s="8" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Y203" s="8" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AA203" t="s">
         <v>54</v>
@@ -10396,78 +10453,78 @@
     </row>
     <row r="204" spans="10:29" ht="15" customHeight="1">
       <c r="J204" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="O204" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="O204" s="8" t="s">
+      <c r="P204" s="7" t="s">
         <v>636</v>
-      </c>
-      <c r="P204" s="7" t="s">
-        <v>637</v>
       </c>
       <c r="Q204" s="8" t="s">
         <v>46</v>
       </c>
       <c r="R204" s="8" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="V204" s="11" t="s">
         <v>52</v>
       </c>
       <c r="W204" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="Y204" s="8" t="s">
         <v>638</v>
-      </c>
-      <c r="Y204" s="8" t="s">
-        <v>639</v>
       </c>
       <c r="AA204" t="s">
         <v>38</v>
       </c>
       <c r="AB204" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="205" spans="10:29" ht="15" customHeight="1">
       <c r="J205" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="O205" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="O205" s="9" t="s">
+      <c r="P205" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q205" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="P205" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="Q205" s="9" t="s">
-        <v>643</v>
-      </c>
       <c r="R205" s="9" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="V205" s="10" t="s">
         <v>37</v>
       </c>
       <c r="W205" s="9"/>
       <c r="Y205" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AA205" t="s">
         <v>54</v>
       </c>
       <c r="AC205" t="s">
-        <v>1301</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="206" spans="10:29" ht="30" customHeight="1">
       <c r="J206" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="O206" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="O206" s="9" t="s">
+      <c r="P206" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="P206" s="10" t="s">
+      <c r="Q206" s="9" t="s">
         <v>647</v>
-      </c>
-      <c r="Q206" s="9" t="s">
-        <v>648</v>
       </c>
       <c r="R206" s="9" t="s">
         <v>76</v>
@@ -10477,7 +10534,7 @@
       </c>
       <c r="W206" s="9"/>
       <c r="Y206" s="9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AA206" t="s">
         <v>54</v>
@@ -10485,46 +10542,46 @@
     </row>
     <row r="207" spans="10:29" ht="30" customHeight="1">
       <c r="J207" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="O207" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="O207" s="9" t="s">
+      <c r="P207" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="P207" s="10" t="s">
+      <c r="Q207" s="9" t="s">
         <v>652</v>
       </c>
-      <c r="Q207" s="9" t="s">
-        <v>653</v>
-      </c>
       <c r="R207" s="9" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="V207" s="10" t="s">
         <v>37</v>
       </c>
       <c r="W207" s="9"/>
       <c r="Y207" s="9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AA207" t="s">
         <v>54</v>
       </c>
       <c r="AC207" t="s">
-        <v>1302</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="208" spans="10:29" ht="30" customHeight="1">
       <c r="J208" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="O208" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="O208" s="9" t="s">
+      <c r="P208" s="10" t="s">
+        <v>1296</v>
+      </c>
+      <c r="Q208" s="9" t="s">
         <v>656</v>
-      </c>
-      <c r="P208" s="10" t="s">
-        <v>1303</v>
-      </c>
-      <c r="Q208" s="9" t="s">
-        <v>657</v>
       </c>
       <c r="R208" s="9" t="s">
         <v>116</v>
@@ -10534,21 +10591,21 @@
       </c>
       <c r="W208" s="9"/>
       <c r="Y208" s="9" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AA208" t="s">
         <v>38</v>
       </c>
       <c r="AB208" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="209" spans="10:28" ht="45" customHeight="1">
       <c r="J209" s="9" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O209" s="9" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>49</v>
@@ -10563,10 +10620,10 @@
         <v>52</v>
       </c>
       <c r="W209" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="Y209" s="9" t="s">
         <v>661</v>
-      </c>
-      <c r="Y209" s="9" t="s">
-        <v>662</v>
       </c>
       <c r="AA209" t="s">
         <v>54</v>
@@ -10574,16 +10631,16 @@
     </row>
     <row r="210" spans="10:28" ht="30" customHeight="1">
       <c r="J210" s="9" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O210" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="P210" s="10" t="s">
+        <v>1297</v>
+      </c>
+      <c r="Q210" s="9" t="s">
         <v>663</v>
-      </c>
-      <c r="P210" s="10" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Q210" s="9" t="s">
-        <v>664</v>
       </c>
       <c r="R210" s="9" t="s">
         <v>65</v>
@@ -10593,24 +10650,24 @@
       </c>
       <c r="W210" s="9"/>
       <c r="Y210" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AA210" t="s">
         <v>38</v>
       </c>
       <c r="AB210" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="211" spans="10:28" ht="30" customHeight="1">
       <c r="J211" s="9" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O211" s="9" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q211" s="9" t="s">
         <v>56</v>
@@ -10619,13 +10676,13 @@
         <v>51</v>
       </c>
       <c r="V211" s="10" t="s">
-        <v>1299</v>
+        <v>1292</v>
       </c>
       <c r="W211" s="9" t="s">
-        <v>1300</v>
+        <v>1293</v>
       </c>
       <c r="Y211" s="9" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AA211" t="s">
         <v>38</v>
@@ -10636,16 +10693,16 @@
     </row>
     <row r="212" spans="10:28" ht="75" customHeight="1">
       <c r="J212" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="O212" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="O212" s="9" t="s">
+      <c r="P212" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q212" s="9" t="s">
         <v>670</v>
-      </c>
-      <c r="P212" s="10" t="s">
-        <v>611</v>
-      </c>
-      <c r="Q212" s="9" t="s">
-        <v>671</v>
       </c>
       <c r="R212" s="9" t="s">
         <v>71</v>
@@ -10654,10 +10711,10 @@
         <v>52</v>
       </c>
       <c r="W212" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="Y212" s="9" t="s">
         <v>672</v>
-      </c>
-      <c r="Y212" s="9" t="s">
-        <v>673</v>
       </c>
       <c r="AA212" t="s">
         <v>54</v>
@@ -10665,16 +10722,16 @@
     </row>
     <row r="213" spans="10:28" ht="15" customHeight="1">
       <c r="J213" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="O213" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="O213" s="9" t="s">
+      <c r="P213" s="10" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q213" s="9" t="s">
         <v>675</v>
-      </c>
-      <c r="P213" s="10" t="s">
-        <v>1276</v>
-      </c>
-      <c r="Q213" s="9" t="s">
-        <v>676</v>
       </c>
       <c r="R213" s="9" t="s">
         <v>116</v>
@@ -10684,27 +10741,27 @@
       </c>
       <c r="W213" s="9"/>
       <c r="Y213" s="9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AA213" t="s">
         <v>38</v>
       </c>
       <c r="AB213" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="214" spans="10:28" ht="15" customHeight="1">
       <c r="J214" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="O214" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="O214" s="9" t="s">
+      <c r="P214" s="10" t="s">
         <v>680</v>
       </c>
-      <c r="P214" s="10" t="s">
+      <c r="Q214" s="9" t="s">
         <v>681</v>
-      </c>
-      <c r="Q214" s="9" t="s">
-        <v>682</v>
       </c>
       <c r="R214" s="9" t="s">
         <v>65</v>
@@ -10714,7 +10771,7 @@
       </c>
       <c r="W214" s="9"/>
       <c r="Y214" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AA214" t="s">
         <v>54</v>
@@ -10722,16 +10779,16 @@
     </row>
     <row r="215" spans="10:28" ht="30" customHeight="1">
       <c r="J215" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="O215" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="O215" s="9" t="s">
+      <c r="P215" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="P215" s="10" t="s">
+      <c r="Q215" s="9" t="s">
         <v>686</v>
-      </c>
-      <c r="Q215" s="9" t="s">
-        <v>687</v>
       </c>
       <c r="R215" s="9" t="s">
         <v>116</v>
@@ -10741,7 +10798,7 @@
       </c>
       <c r="W215" s="9"/>
       <c r="Y215" s="9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="AA215" t="s">
         <v>54</v>
@@ -10749,16 +10806,16 @@
     </row>
     <row r="216" spans="10:28" ht="30" customHeight="1">
       <c r="J216" s="9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="O216" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="P216" s="10" t="s">
         <v>114</v>
       </c>
       <c r="Q216" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="R216" s="9" t="s">
         <v>116</v>
@@ -10768,7 +10825,7 @@
       </c>
       <c r="W216" s="9"/>
       <c r="Y216" s="9" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AA216" t="s">
         <v>54</v>
@@ -10776,16 +10833,16 @@
     </row>
     <row r="217" spans="10:28" ht="30" customHeight="1">
       <c r="J217" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="O217" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="O217" s="9" t="s">
+      <c r="P217" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="P217" s="10" t="s">
+      <c r="Q217" s="9" t="s">
         <v>694</v>
-      </c>
-      <c r="Q217" s="9" t="s">
-        <v>695</v>
       </c>
       <c r="R217" s="9" t="s">
         <v>71</v>
@@ -10794,10 +10851,10 @@
         <v>52</v>
       </c>
       <c r="W217" s="9" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="Y217" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AA217" t="s">
         <v>54</v>
@@ -10805,16 +10862,16 @@
     </row>
     <row r="218" spans="10:28" ht="45" customHeight="1">
       <c r="J218" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O218" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="P218" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="Q218" s="9" t="s">
         <v>697</v>
-      </c>
-      <c r="P218" s="10" t="s">
-        <v>694</v>
-      </c>
-      <c r="Q218" s="9" t="s">
-        <v>698</v>
       </c>
       <c r="R218" s="9" t="s">
         <v>71</v>
@@ -10823,10 +10880,10 @@
         <v>52</v>
       </c>
       <c r="W218" s="9" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="Y218" s="9" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AA218" t="s">
         <v>54</v>
@@ -10834,13 +10891,13 @@
     </row>
     <row r="219" spans="10:28" ht="30" customHeight="1">
       <c r="J219" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O219" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="P219" s="7" t="s">
         <v>700</v>
-      </c>
-      <c r="P219" s="7" t="s">
-        <v>701</v>
       </c>
       <c r="Q219" s="8">
         <v>1</v>
@@ -10853,27 +10910,27 @@
       </c>
       <c r="W219" s="8"/>
       <c r="Y219" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AA219" t="s">
         <v>38</v>
       </c>
       <c r="AB219" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="220" spans="10:28" ht="45" customHeight="1">
       <c r="J220" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O220" s="8" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="P220" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="Q220" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="R220" s="8" t="s">
         <v>71</v>
@@ -10882,10 +10939,10 @@
         <v>52</v>
       </c>
       <c r="W220" s="8" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="Y220" s="8" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AA220" t="s">
         <v>54</v>
@@ -10893,16 +10950,16 @@
     </row>
     <row r="221" spans="10:28" ht="45" customHeight="1">
       <c r="J221" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O221" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P221" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="Q221" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="R221" s="8" t="s">
         <v>71</v>
@@ -10911,10 +10968,10 @@
         <v>52</v>
       </c>
       <c r="W221" s="8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="Y221" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AA221" t="s">
         <v>54</v>
@@ -10922,13 +10979,13 @@
     </row>
     <row r="222" spans="10:28" ht="30" customHeight="1">
       <c r="J222" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O222" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="P222" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="Q222" s="8">
         <v>1</v>
@@ -10941,27 +10998,27 @@
       </c>
       <c r="W222" s="8"/>
       <c r="Y222" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AA222" t="s">
         <v>38</v>
       </c>
       <c r="AB222" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="223" spans="10:28" ht="360" customHeight="1">
       <c r="J223" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="O223" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="O223" s="8" t="s">
+      <c r="P223" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="Q223" s="8" t="s">
         <v>709</v>
-      </c>
-      <c r="P223" s="7" t="s">
-        <v>694</v>
-      </c>
-      <c r="Q223" s="8" t="s">
-        <v>710</v>
       </c>
       <c r="R223" s="8" t="s">
         <v>71</v>
@@ -10970,10 +11027,10 @@
         <v>52</v>
       </c>
       <c r="W223" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="Y223" s="8" t="s">
         <v>711</v>
-      </c>
-      <c r="Y223" s="8" t="s">
-        <v>712</v>
       </c>
       <c r="AA223" t="s">
         <v>54</v>
@@ -10981,16 +11038,16 @@
     </row>
     <row r="224" spans="10:28" ht="30" customHeight="1">
       <c r="J224" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="O224" s="8" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="P224" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="Q224" s="8" t="s">
         <v>694</v>
-      </c>
-      <c r="Q224" s="8" t="s">
-        <v>695</v>
       </c>
       <c r="R224" s="8" t="s">
         <v>71</v>
@@ -10999,10 +11056,10 @@
         <v>52</v>
       </c>
       <c r="W224" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="Y224" s="8" t="s">
         <v>714</v>
-      </c>
-      <c r="Y224" s="8" t="s">
-        <v>715</v>
       </c>
       <c r="AA224" t="s">
         <v>54</v>
@@ -11010,16 +11067,16 @@
     </row>
     <row r="225" spans="10:29" ht="15" customHeight="1">
       <c r="J225" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="O225" s="8" t="s">
         <v>716</v>
-      </c>
-      <c r="O225" s="8" t="s">
-        <v>717</v>
       </c>
       <c r="P225" s="7" t="s">
         <v>183</v>
       </c>
       <c r="Q225" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="R225" s="8" t="s">
         <v>36</v>
@@ -11029,7 +11086,7 @@
       </c>
       <c r="W225" s="8"/>
       <c r="Y225" s="8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AA225" t="s">
         <v>54</v>
@@ -11037,16 +11094,16 @@
     </row>
     <row r="226" spans="10:29" ht="15" customHeight="1">
       <c r="J226" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="O226" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="O226" s="8" t="s">
+      <c r="P226" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="P226" s="7" t="s">
+      <c r="Q226" s="8" t="s">
         <v>722</v>
-      </c>
-      <c r="Q226" s="8" t="s">
-        <v>723</v>
       </c>
       <c r="R226" s="8" t="s">
         <v>36</v>
@@ -11056,7 +11113,7 @@
       </c>
       <c r="W226" s="8"/>
       <c r="Y226" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AA226" t="s">
         <v>54</v>
@@ -11064,16 +11121,16 @@
     </row>
     <row r="227" spans="10:29" ht="15" customHeight="1">
       <c r="J227" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="O227" s="8" t="s">
         <v>725</v>
       </c>
-      <c r="O227" s="8" t="s">
+      <c r="P227" s="7" t="s">
         <v>726</v>
       </c>
-      <c r="P227" s="7" t="s">
+      <c r="Q227" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="Q227" s="8" t="s">
-        <v>728</v>
       </c>
       <c r="R227" s="8" t="s">
         <v>36</v>
@@ -11083,7 +11140,7 @@
       </c>
       <c r="W227" s="8"/>
       <c r="Y227" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AA227" t="s">
         <v>54</v>
@@ -11091,13 +11148,13 @@
     </row>
     <row r="228" spans="10:29" ht="45" customHeight="1">
       <c r="J228" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="O228" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="O228" s="8" t="s">
-        <v>731</v>
-      </c>
       <c r="P228" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="Q228" s="8" t="s">
         <v>50</v>
@@ -11109,10 +11166,10 @@
         <v>52</v>
       </c>
       <c r="W228" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="Y228" s="8" t="s">
         <v>732</v>
-      </c>
-      <c r="Y228" s="8" t="s">
-        <v>733</v>
       </c>
       <c r="AA228" t="s">
         <v>54</v>
@@ -11120,16 +11177,16 @@
     </row>
     <row r="229" spans="10:29" ht="15" customHeight="1">
       <c r="J229" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O229" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="P229" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="P229" s="7" t="s">
+      <c r="Q229" s="8" t="s">
         <v>735</v>
-      </c>
-      <c r="Q229" s="8" t="s">
-        <v>736</v>
       </c>
       <c r="R229" s="8" t="s">
         <v>65</v>
@@ -11139,7 +11196,7 @@
       </c>
       <c r="W229" s="8"/>
       <c r="Y229" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AA229" t="s">
         <v>54</v>
@@ -11147,10 +11204,10 @@
     </row>
     <row r="230" spans="10:29" ht="45" customHeight="1">
       <c r="J230" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O230" s="8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="P230" s="7" t="s">
         <v>595</v>
@@ -11165,10 +11222,10 @@
         <v>52</v>
       </c>
       <c r="W230" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y230" s="8" t="s">
         <v>739</v>
-      </c>
-      <c r="Y230" s="8" t="s">
-        <v>740</v>
       </c>
       <c r="AA230" t="s">
         <v>54</v>
@@ -11176,13 +11233,13 @@
     </row>
     <row r="231" spans="10:29" ht="30" customHeight="1">
       <c r="J231" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O231" s="8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="P231" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="Q231" s="8" t="s">
         <v>56</v>
@@ -11194,10 +11251,10 @@
         <v>52</v>
       </c>
       <c r="W231" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y231" s="8" t="s">
         <v>742</v>
-      </c>
-      <c r="Y231" s="8" t="s">
-        <v>743</v>
       </c>
       <c r="AA231" t="s">
         <v>54</v>
@@ -11205,16 +11262,16 @@
     </row>
     <row r="232" spans="10:29" ht="30" customHeight="1">
       <c r="J232" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O232" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="P232" s="7" t="s">
         <v>204</v>
       </c>
       <c r="Q232" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="R232" s="8" t="s">
         <v>116</v>
@@ -11224,24 +11281,24 @@
       </c>
       <c r="W232" s="8"/>
       <c r="Y232" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="AA232" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC232" t="s">
         <v>746</v>
-      </c>
-      <c r="AA232" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC232" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="233" spans="10:29" ht="30" customHeight="1">
       <c r="J233" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O233" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="P233" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="Q233" s="8" t="s">
         <v>50</v>
@@ -11253,10 +11310,10 @@
         <v>52</v>
       </c>
       <c r="W233" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="Y233" s="8" t="s">
         <v>749</v>
-      </c>
-      <c r="Y233" s="8" t="s">
-        <v>750</v>
       </c>
       <c r="AA233" t="s">
         <v>54</v>
@@ -11264,10 +11321,10 @@
     </row>
     <row r="234" spans="10:29" ht="30" customHeight="1">
       <c r="J234" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O234" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="P234" s="7" t="s">
         <v>354</v>
@@ -11283,7 +11340,7 @@
       </c>
       <c r="W234" s="8"/>
       <c r="Y234" s="8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AA234" t="s">
         <v>54</v>
@@ -11291,16 +11348,16 @@
     </row>
     <row r="235" spans="10:29">
       <c r="J235" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O235" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="P235" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="P235" s="12" t="s">
+      <c r="Q235" s="12" t="s">
         <v>754</v>
-      </c>
-      <c r="Q235" s="12" t="s">
-        <v>755</v>
       </c>
       <c r="R235" s="12" t="s">
         <v>36</v>
@@ -11310,27 +11367,27 @@
       </c>
       <c r="W235" s="12"/>
       <c r="Y235" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="AA235" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC235" t="s">
         <v>756</v>
-      </c>
-      <c r="AA235" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC235" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="236" spans="10:29">
       <c r="J236" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O236" s="12" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="P236" s="12" t="s">
         <v>354</v>
       </c>
       <c r="Q236" s="12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="R236" s="12" t="s">
         <v>65</v>
@@ -11340,7 +11397,7 @@
       </c>
       <c r="W236" s="12"/>
       <c r="Y236" s="12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AA236" t="s">
         <v>54</v>
@@ -11348,10 +11405,10 @@
     </row>
     <row r="237" spans="10:29" ht="28.8">
       <c r="J237" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O237" s="12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P237" s="12" t="s">
         <v>49</v>
@@ -11366,10 +11423,10 @@
         <v>52</v>
       </c>
       <c r="W237" s="12" t="s">
+        <v>761</v>
+      </c>
+      <c r="Y237" s="12" t="s">
         <v>762</v>
-      </c>
-      <c r="Y237" s="12" t="s">
-        <v>763</v>
       </c>
       <c r="AA237" t="s">
         <v>54</v>
@@ -11377,45 +11434,45 @@
     </row>
     <row r="238" spans="10:29">
       <c r="J238" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O238" s="12" t="s">
+        <v>763</v>
+      </c>
+      <c r="P238" s="12" t="s">
         <v>764</v>
       </c>
-      <c r="P238" s="12" t="s">
+      <c r="Q238" s="12" t="s">
         <v>765</v>
       </c>
-      <c r="Q238" s="12" t="s">
+      <c r="R238" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="V238" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y238" s="12" t="s">
         <v>766</v>
       </c>
-      <c r="R238" s="12" t="s">
-        <v>1305</v>
-      </c>
-      <c r="V238" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y238" s="12" t="s">
+      <c r="AA238" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC238" t="s">
         <v>767</v>
-      </c>
-      <c r="AA238" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC238" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="239" spans="10:29" ht="28.8" customHeight="1">
       <c r="J239" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O239" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="P239" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="P239" s="12" t="s">
+      <c r="Q239" s="12" t="s">
         <v>770</v>
-      </c>
-      <c r="Q239" s="12" t="s">
-        <v>771</v>
       </c>
       <c r="R239" s="12" t="s">
         <v>116</v>
@@ -11424,7 +11481,7 @@
         <v>37</v>
       </c>
       <c r="Y239" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AA239" t="s">
         <v>54</v>
@@ -11432,16 +11489,16 @@
     </row>
     <row r="240" spans="10:29" ht="28.8" customHeight="1">
       <c r="J240" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O240" s="12" t="s">
+        <v>772</v>
+      </c>
+      <c r="P240" s="12" t="s">
+        <v>769</v>
+      </c>
+      <c r="Q240" s="12" t="s">
         <v>773</v>
-      </c>
-      <c r="P240" s="12" t="s">
-        <v>770</v>
-      </c>
-      <c r="Q240" s="12" t="s">
-        <v>774</v>
       </c>
       <c r="R240" s="12" t="s">
         <v>116</v>
@@ -11450,7 +11507,7 @@
         <v>37</v>
       </c>
       <c r="Y240" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AA240" t="s">
         <v>54</v>
@@ -11458,16 +11515,16 @@
     </row>
     <row r="241" spans="10:29" ht="28.8" customHeight="1">
       <c r="J241" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O241" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="P241" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="P241" s="12" t="s">
+      <c r="Q241" s="12" t="s">
         <v>777</v>
-      </c>
-      <c r="Q241" s="12" t="s">
-        <v>778</v>
       </c>
       <c r="R241" s="12" t="s">
         <v>116</v>
@@ -11476,85 +11533,85 @@
         <v>37</v>
       </c>
       <c r="Y241" s="12" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AA241" t="s">
         <v>54</v>
       </c>
       <c r="AC241" t="s">
-        <v>1306</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="242" spans="10:29">
       <c r="J242" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O242" s="12" t="s">
+        <v>779</v>
+      </c>
+      <c r="P242" s="12" t="s">
         <v>780</v>
       </c>
-      <c r="P242" s="12" t="s">
+      <c r="Q242" s="12" t="s">
         <v>781</v>
       </c>
-      <c r="Q242" s="12" t="s">
+      <c r="R242" s="12" t="s">
+        <v>1271</v>
+      </c>
+      <c r="V242" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y242" s="12" t="s">
         <v>782</v>
       </c>
-      <c r="R242" s="12" t="s">
-        <v>1278</v>
-      </c>
-      <c r="V242" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y242" s="12" t="s">
-        <v>783</v>
-      </c>
       <c r="AA242" t="s">
         <v>54</v>
       </c>
       <c r="AC242" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="243" spans="10:29">
       <c r="J243" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O243" s="12" t="s">
+        <v>783</v>
+      </c>
+      <c r="P243" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q243" s="12" t="s">
         <v>784</v>
       </c>
-      <c r="P243" s="12" t="s">
-        <v>781</v>
-      </c>
-      <c r="Q243" s="12" t="s">
+      <c r="R243" s="12" t="s">
+        <v>1271</v>
+      </c>
+      <c r="V243" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y243" s="12" t="s">
         <v>785</v>
       </c>
-      <c r="R243" s="12" t="s">
-        <v>1278</v>
-      </c>
-      <c r="V243" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y243" s="12" t="s">
+      <c r="AA243" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC243" t="s">
         <v>786</v>
-      </c>
-      <c r="AA243" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC243" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="244" spans="10:29" ht="28.8" customHeight="1">
       <c r="J244" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O244" s="12" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P244" s="12" t="s">
         <v>155</v>
       </c>
       <c r="Q244" s="12" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="R244" s="12" t="s">
         <v>116</v>
@@ -11563,7 +11620,7 @@
         <v>37</v>
       </c>
       <c r="Y244" s="12" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AA244" t="s">
         <v>54</v>
@@ -11571,16 +11628,16 @@
     </row>
     <row r="245" spans="10:29" ht="28.8" customHeight="1">
       <c r="J245" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O245" s="12" t="s">
+        <v>790</v>
+      </c>
+      <c r="P245" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="Q245" s="12" t="s">
         <v>791</v>
-      </c>
-      <c r="P245" s="12" t="s">
-        <v>647</v>
-      </c>
-      <c r="Q245" s="12" t="s">
-        <v>792</v>
       </c>
       <c r="R245" s="12" t="s">
         <v>76</v>
@@ -11589,7 +11646,7 @@
         <v>37</v>
       </c>
       <c r="Y245" s="12" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AA245" t="s">
         <v>54</v>
@@ -11597,16 +11654,16 @@
     </row>
     <row r="246" spans="10:29" ht="28.8" customHeight="1">
       <c r="J246" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O246" s="12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P246" s="12" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q246" s="12" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="R246" s="12" t="s">
         <v>76</v>
@@ -11615,7 +11672,7 @@
         <v>37</v>
       </c>
       <c r="Y246" s="12" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AA246" t="s">
         <v>54</v>
@@ -11623,16 +11680,16 @@
     </row>
     <row r="247" spans="10:29">
       <c r="J247" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O247" s="12" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P247" s="12" t="s">
         <v>493</v>
       </c>
       <c r="Q247" s="12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="R247" s="12" t="s">
         <v>65</v>
@@ -11641,7 +11698,7 @@
         <v>37</v>
       </c>
       <c r="Y247" s="12" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA247" t="s">
         <v>54</v>
@@ -11649,16 +11706,16 @@
     </row>
     <row r="248" spans="10:29" ht="28.8" customHeight="1">
       <c r="J248" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O248" s="12" t="s">
         <v>261</v>
       </c>
       <c r="P248" s="12" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q248" s="12" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="R248" s="12" t="s">
         <v>76</v>
@@ -11667,7 +11724,7 @@
         <v>37</v>
       </c>
       <c r="Y248" s="12" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AA248" t="s">
         <v>54</v>
@@ -11675,16 +11732,16 @@
     </row>
     <row r="249" spans="10:29" ht="28.8" customHeight="1">
       <c r="J249" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O249" s="12" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="P249" s="12" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q249" s="12" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="R249" s="12" t="s">
         <v>76</v>
@@ -11693,7 +11750,7 @@
         <v>37</v>
       </c>
       <c r="Y249" s="12" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AA249" t="s">
         <v>54</v>
@@ -11701,16 +11758,16 @@
     </row>
     <row r="250" spans="10:29" ht="28.8" customHeight="1">
       <c r="J250" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O250" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="P250" s="12" t="s">
         <v>801</v>
       </c>
-      <c r="P250" s="12" t="s">
+      <c r="Q250" s="12" t="s">
         <v>802</v>
-      </c>
-      <c r="Q250" s="12" t="s">
-        <v>803</v>
       </c>
       <c r="R250" s="12" t="s">
         <v>116</v>
@@ -11719,7 +11776,7 @@
         <v>37</v>
       </c>
       <c r="Y250" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AA250" t="s">
         <v>54</v>
@@ -11727,16 +11784,16 @@
     </row>
     <row r="251" spans="10:29" ht="28.8" customHeight="1">
       <c r="J251" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O251" s="12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="P251" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="Q251" s="12" t="s">
         <v>802</v>
-      </c>
-      <c r="Q251" s="12" t="s">
-        <v>803</v>
       </c>
       <c r="R251" s="12" t="s">
         <v>116</v>
@@ -11745,7 +11802,7 @@
         <v>37</v>
       </c>
       <c r="Y251" s="12" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AA251" t="s">
         <v>54</v>
@@ -11753,16 +11810,16 @@
     </row>
     <row r="252" spans="10:29">
       <c r="J252" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O252" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="P252" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q252" s="12" t="s">
         <v>807</v>
-      </c>
-      <c r="P252" s="12" t="s">
-        <v>781</v>
-      </c>
-      <c r="Q252" s="12" t="s">
-        <v>808</v>
       </c>
       <c r="R252" s="12" t="s">
         <v>65</v>
@@ -11771,7 +11828,7 @@
         <v>37</v>
       </c>
       <c r="Y252" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AA252" t="s">
         <v>54</v>
@@ -11779,16 +11836,16 @@
     </row>
     <row r="253" spans="10:29">
       <c r="J253" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O253" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="P253" s="12" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="Q253" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="R253" s="12" t="s">
         <v>65</v>
@@ -11797,7 +11854,7 @@
         <v>37</v>
       </c>
       <c r="Y253" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AA253" t="s">
         <v>54</v>
@@ -11805,10 +11862,10 @@
     </row>
     <row r="254" spans="10:29">
       <c r="J254" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O254" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="P254" s="12" t="s">
         <v>354</v>
@@ -11823,7 +11880,7 @@
         <v>37</v>
       </c>
       <c r="Y254" s="12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AA254" t="s">
         <v>54</v>
@@ -11831,16 +11888,16 @@
     </row>
     <row r="255" spans="10:29" ht="30" customHeight="1">
       <c r="J255" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O255" s="13" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="P255" s="14" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q255" s="13" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="R255" s="13" t="s">
         <v>76</v>
@@ -11850,7 +11907,7 @@
       </c>
       <c r="W255" s="13"/>
       <c r="Y255" s="13" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AA255" t="s">
         <v>54</v>
@@ -11858,46 +11915,46 @@
     </row>
     <row r="256" spans="10:29" ht="30" customHeight="1">
       <c r="J256" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O256" s="13" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="P256" s="14" t="s">
         <v>364</v>
       </c>
       <c r="Q256" s="13" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="R256" s="13" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="V256" s="14" t="s">
         <v>37</v>
       </c>
       <c r="W256" s="13"/>
       <c r="Y256" s="13" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="AA256" t="s">
         <v>54</v>
       </c>
       <c r="AC256" t="s">
-        <v>1308</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="257" spans="10:28" ht="30" customHeight="1">
       <c r="J257" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O257" s="13" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="P257" s="14" t="s">
         <v>155</v>
       </c>
       <c r="Q257" s="13" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="R257" s="13" t="s">
         <v>116</v>
@@ -11907,7 +11964,7 @@
       </c>
       <c r="W257" s="13"/>
       <c r="Y257" s="13" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AA257" t="s">
         <v>54</v>
@@ -11915,16 +11972,16 @@
     </row>
     <row r="258" spans="10:28" ht="15" customHeight="1">
       <c r="J258" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="O258" s="13" t="s">
+        <v>820</v>
+      </c>
+      <c r="P258" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q258" s="13" t="s">
         <v>821</v>
-      </c>
-      <c r="P258" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Q258" s="13" t="s">
-        <v>822</v>
       </c>
       <c r="R258" s="13" t="s">
         <v>65</v>
@@ -11934,7 +11991,7 @@
       </c>
       <c r="W258" s="13"/>
       <c r="Y258" s="13" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AA258" t="s">
         <v>54</v>
@@ -11942,10 +11999,10 @@
     </row>
     <row r="259" spans="10:28" ht="15" customHeight="1">
       <c r="J259" s="13" t="s">
+        <v>823</v>
+      </c>
+      <c r="O259" s="13" t="s">
         <v>824</v>
-      </c>
-      <c r="O259" s="13" t="s">
-        <v>825</v>
       </c>
       <c r="P259" s="14" t="s">
         <v>354</v>
@@ -11961,7 +12018,7 @@
       </c>
       <c r="W259" s="13"/>
       <c r="Y259" s="13" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AA259" t="s">
         <v>54</v>
@@ -11969,16 +12026,16 @@
     </row>
     <row r="260" spans="10:28" ht="30" customHeight="1">
       <c r="J260" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O260" s="13" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="P260" s="14" t="s">
         <v>155</v>
       </c>
       <c r="Q260" s="13" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="R260" s="13" t="s">
         <v>116</v>
@@ -11988,7 +12045,7 @@
       </c>
       <c r="W260" s="13"/>
       <c r="Y260" s="13" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AA260" t="s">
         <v>54</v>
@@ -11996,13 +12053,13 @@
     </row>
     <row r="261" spans="10:28" ht="30" customHeight="1">
       <c r="J261" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O261" s="13" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="P261" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q261" s="13" t="s">
         <v>56</v>
@@ -12014,10 +12071,10 @@
         <v>52</v>
       </c>
       <c r="W261" s="13" t="s">
+        <v>830</v>
+      </c>
+      <c r="Y261" s="13" t="s">
         <v>831</v>
-      </c>
-      <c r="Y261" s="13" t="s">
-        <v>832</v>
       </c>
       <c r="AA261" t="s">
         <v>54</v>
@@ -12025,13 +12082,13 @@
     </row>
     <row r="262" spans="10:28" ht="15" customHeight="1">
       <c r="J262" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O262" s="13" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P262" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q262" s="13" t="s">
         <v>56</v>
@@ -12043,10 +12100,10 @@
         <v>52</v>
       </c>
       <c r="W262" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="Y262" s="13" t="s">
         <v>834</v>
-      </c>
-      <c r="Y262" s="13" t="s">
-        <v>835</v>
       </c>
       <c r="AA262" t="s">
         <v>54</v>
@@ -12054,16 +12111,16 @@
     </row>
     <row r="263" spans="10:28" ht="30" customHeight="1">
       <c r="J263" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O263" s="13" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="P263" s="14" t="s">
         <v>308</v>
       </c>
       <c r="Q263" s="13" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="R263" s="13" t="s">
         <v>116</v>
@@ -12073,7 +12130,7 @@
       </c>
       <c r="W263" s="13"/>
       <c r="Y263" s="13" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AA263" t="s">
         <v>54</v>
@@ -12081,16 +12138,16 @@
     </row>
     <row r="264" spans="10:28" ht="30" customHeight="1">
       <c r="J264" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O264" s="13" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P264" s="14" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
       <c r="Q264" s="13" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="R264" s="13" t="s">
         <v>76</v>
@@ -12100,27 +12157,27 @@
       </c>
       <c r="W264" s="13"/>
       <c r="Y264" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA264" t="s">
         <v>38</v>
       </c>
       <c r="AB264" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="265" spans="10:28" ht="30" customHeight="1">
       <c r="J265" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O265" s="13" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P265" s="14" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q265" s="13" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="R265" s="13" t="s">
         <v>76</v>
@@ -12130,7 +12187,7 @@
       </c>
       <c r="W265" s="13"/>
       <c r="Y265" s="13" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AA265" t="s">
         <v>54</v>
@@ -12138,10 +12195,10 @@
     </row>
     <row r="266" spans="10:28" ht="30" customHeight="1">
       <c r="J266" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O266" s="13" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="P266" s="14" t="s">
         <v>59</v>
@@ -12156,10 +12213,10 @@
         <v>52</v>
       </c>
       <c r="W266" s="13" t="s">
+        <v>844</v>
+      </c>
+      <c r="Y266" s="13" t="s">
         <v>845</v>
-      </c>
-      <c r="Y266" s="13" t="s">
-        <v>846</v>
       </c>
       <c r="AA266" t="s">
         <v>54</v>
@@ -12167,16 +12224,16 @@
     </row>
     <row r="267" spans="10:28" ht="30" customHeight="1">
       <c r="J267" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O267" s="13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="P267" s="14" t="s">
         <v>308</v>
       </c>
       <c r="Q267" s="13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="R267" s="13" t="s">
         <v>116</v>
@@ -12186,7 +12243,7 @@
       </c>
       <c r="W267" s="13"/>
       <c r="Y267" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AA267" t="s">
         <v>54</v>
@@ -12194,16 +12251,16 @@
     </row>
     <row r="268" spans="10:28" ht="30" customHeight="1">
       <c r="J268" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O268" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="P268" s="14" t="s">
         <v>155</v>
       </c>
       <c r="Q268" s="13" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R268" s="13" t="s">
         <v>116</v>
@@ -12213,7 +12270,7 @@
       </c>
       <c r="W268" s="13"/>
       <c r="Y268" s="13" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AA268" t="s">
         <v>54</v>
@@ -12221,13 +12278,13 @@
     </row>
     <row r="269" spans="10:28" ht="15" customHeight="1">
       <c r="J269" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O269" s="13" t="s">
+        <v>852</v>
+      </c>
+      <c r="P269" s="14" t="s">
         <v>853</v>
-      </c>
-      <c r="P269" s="14" t="s">
-        <v>854</v>
       </c>
       <c r="Q269" s="13" t="s">
         <v>56</v>
@@ -12240,7 +12297,7 @@
       </c>
       <c r="W269" s="13"/>
       <c r="Y269" s="13" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AA269" t="s">
         <v>54</v>
@@ -12248,70 +12305,70 @@
     </row>
     <row r="270" spans="10:28" ht="30" customHeight="1">
       <c r="J270" s="13" t="s">
+        <v>855</v>
+      </c>
+      <c r="O270" s="13" t="s">
         <v>856</v>
       </c>
-      <c r="O270" s="13" t="s">
+      <c r="P270" s="14" t="s">
         <v>857</v>
-      </c>
-      <c r="P270" s="14" t="s">
-        <v>858</v>
       </c>
       <c r="Q270" s="13" t="s">
         <v>56</v>
       </c>
       <c r="R270" s="13" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="V270" s="14" t="s">
         <v>37</v>
       </c>
       <c r="W270" s="13"/>
       <c r="Y270" s="13" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AA270" t="s">
         <v>38</v>
       </c>
       <c r="AB270" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="271" spans="10:28" ht="30" customHeight="1">
       <c r="J271" s="13" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O271" s="13" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="P271" s="14" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="Q271" s="13" t="s">
         <v>56</v>
       </c>
       <c r="R271" s="13" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="V271" s="14" t="s">
         <v>37</v>
       </c>
       <c r="W271" s="13"/>
       <c r="Y271" s="13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AA271" t="s">
         <v>38</v>
       </c>
       <c r="AB271" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="272" spans="10:28" ht="15" customHeight="1">
       <c r="J272" s="13" t="s">
+        <v>862</v>
+      </c>
+      <c r="O272" s="13" t="s">
         <v>863</v>
-      </c>
-      <c r="O272" s="13" t="s">
-        <v>864</v>
       </c>
       <c r="P272" s="14" t="s">
         <v>42</v>
@@ -12327,7 +12384,7 @@
       </c>
       <c r="W272" s="13"/>
       <c r="Y272" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="AA272" t="s">
         <v>54</v>
@@ -12335,10 +12392,10 @@
     </row>
     <row r="273" spans="10:29" ht="15" customHeight="1">
       <c r="J273" s="13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="O273" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="P273" s="14" t="s">
         <v>42</v>
@@ -12354,7 +12411,7 @@
       </c>
       <c r="W273" s="13"/>
       <c r="Y273" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="AA273" t="s">
         <v>54</v>
@@ -12362,10 +12419,10 @@
     </row>
     <row r="274" spans="10:29" ht="15" customHeight="1">
       <c r="J274" s="13" t="s">
+        <v>867</v>
+      </c>
+      <c r="O274" s="13" t="s">
         <v>868</v>
-      </c>
-      <c r="O274" s="13" t="s">
-        <v>869</v>
       </c>
       <c r="P274" s="14" t="s">
         <v>42</v>
@@ -12381,27 +12438,27 @@
       </c>
       <c r="W274" s="13"/>
       <c r="Y274" s="13" t="s">
-        <v>1310</v>
+        <v>1303</v>
       </c>
       <c r="AA274" t="s">
         <v>38</v>
       </c>
       <c r="AB274" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="275" spans="10:29" s="15" customFormat="1" ht="30" customHeight="1">
       <c r="J275" s="8" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O275" s="8" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="P275" s="7" t="s">
-        <v>1311</v>
+        <v>1304</v>
       </c>
       <c r="Q275" s="8" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="R275" s="8" t="s">
         <v>116</v>
@@ -12411,28 +12468,28 @@
       </c>
       <c r="W275" s="8"/>
       <c r="Y275" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AA275" t="s">
         <v>38</v>
       </c>
       <c r="AB275" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AC275"/>
     </row>
     <row r="276" spans="10:29" s="15" customFormat="1" ht="30" customHeight="1">
       <c r="J276" s="8" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O276" s="8" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="P276" s="7" t="s">
-        <v>1311</v>
+        <v>1304</v>
       </c>
       <c r="Q276" s="8" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="R276" s="8" t="s">
         <v>116</v>
@@ -12442,28 +12499,28 @@
       </c>
       <c r="W276" s="8"/>
       <c r="Y276" s="8" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="AA276" t="s">
         <v>38</v>
       </c>
       <c r="AB276" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AC276"/>
     </row>
     <row r="277" spans="10:29" ht="165" customHeight="1">
       <c r="J277" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="O277" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="O277" s="8" t="s">
+      <c r="P277" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="P277" s="7" t="s">
+      <c r="Q277" s="8" t="s">
         <v>879</v>
-      </c>
-      <c r="Q277" s="8" t="s">
-        <v>880</v>
       </c>
       <c r="R277" s="8" t="s">
         <v>71</v>
@@ -12472,10 +12529,10 @@
         <v>52</v>
       </c>
       <c r="W277" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="Y277" s="8" t="s">
         <v>881</v>
-      </c>
-      <c r="Y277" s="8" t="s">
-        <v>882</v>
       </c>
       <c r="AA277" t="s">
         <v>54</v>
@@ -12483,16 +12540,16 @@
     </row>
     <row r="278" spans="10:29" ht="30" customHeight="1">
       <c r="J278" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="O278" s="8" t="s">
         <v>883</v>
-      </c>
-      <c r="O278" s="8" t="s">
-        <v>884</v>
       </c>
       <c r="P278" s="7" t="s">
         <v>204</v>
       </c>
       <c r="Q278" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="R278" s="8" t="s">
         <v>116</v>
@@ -12502,7 +12559,7 @@
       </c>
       <c r="W278" s="8"/>
       <c r="Y278" s="8" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AA278" t="s">
         <v>54</v>
@@ -12510,16 +12567,16 @@
     </row>
     <row r="279" spans="10:29" ht="15" customHeight="1">
       <c r="J279" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="O279" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="O279" s="8" t="s">
-        <v>887</v>
-      </c>
       <c r="P279" s="7" t="s">
-        <v>1312</v>
+        <v>1305</v>
       </c>
       <c r="Q279" s="8" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="R279" s="8" t="s">
         <v>116</v>
@@ -12529,27 +12586,27 @@
       </c>
       <c r="W279" s="8"/>
       <c r="Y279" s="8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="AA279" t="s">
         <v>38</v>
       </c>
       <c r="AB279" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="280" spans="10:29" ht="15" customHeight="1">
       <c r="J280" s="8" t="s">
+        <v>889</v>
+      </c>
+      <c r="O280" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="O280" s="8" t="s">
+      <c r="P280" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q280" s="8" t="s">
         <v>891</v>
-      </c>
-      <c r="P280" s="7" t="s">
-        <v>1276</v>
-      </c>
-      <c r="Q280" s="8" t="s">
-        <v>892</v>
       </c>
       <c r="R280" s="8" t="s">
         <v>116</v>
@@ -12559,27 +12616,27 @@
       </c>
       <c r="W280" s="8"/>
       <c r="Y280" s="8" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AA280" t="s">
         <v>38</v>
       </c>
       <c r="AB280" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="281" spans="10:29" ht="15" customHeight="1">
       <c r="J281" s="8" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="O281" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="P281" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q281" s="8" t="s">
         <v>895</v>
-      </c>
-      <c r="P281" s="7" t="s">
-        <v>1276</v>
-      </c>
-      <c r="Q281" s="8" t="s">
-        <v>896</v>
       </c>
       <c r="R281" s="8" t="s">
         <v>116</v>
@@ -12589,27 +12646,27 @@
       </c>
       <c r="W281" s="8"/>
       <c r="Y281" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="AA281" t="s">
         <v>38</v>
       </c>
       <c r="AB281" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="282" spans="10:29" ht="15" customHeight="1">
       <c r="J282" s="8" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="O282" s="8" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="P282" s="7" t="s">
-        <v>1313</v>
+        <v>1306</v>
       </c>
       <c r="Q282" s="8" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="R282" s="8" t="s">
         <v>116</v>
@@ -12619,27 +12676,27 @@
       </c>
       <c r="W282" s="8"/>
       <c r="Y282" s="8" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="AA282" t="s">
         <v>38</v>
       </c>
       <c r="AB282" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="283" spans="10:29" ht="15" customHeight="1">
       <c r="J283" s="8" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="O283" s="8" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="P283" s="7" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="Q283" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="R283" s="8" t="s">
         <v>116</v>
@@ -12649,21 +12706,21 @@
       </c>
       <c r="W283" s="8"/>
       <c r="Y283" s="8" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="AA283" t="s">
         <v>38</v>
       </c>
       <c r="AB283" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="284" spans="10:29" ht="30" customHeight="1">
       <c r="J284" s="8" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="O284" s="8" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="P284" s="7" t="s">
         <v>63</v>
@@ -12679,7 +12736,7 @@
       </c>
       <c r="W284" s="8"/>
       <c r="Y284" s="8" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="AA284" t="s">
         <v>54</v>
@@ -12687,13 +12744,13 @@
     </row>
     <row r="285" spans="10:29" ht="30" customHeight="1">
       <c r="J285" s="8" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="O285" s="8" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="P285" s="7" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="Q285" s="8" t="s">
         <v>56</v>
@@ -12706,54 +12763,54 @@
       </c>
       <c r="W285" s="8"/>
       <c r="Y285" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="AA285" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="286" spans="10:29" s="18" customFormat="1" ht="15" customHeight="1">
+      <c r="J286" s="31" t="s">
+        <v>910</v>
+      </c>
+      <c r="O286" s="31" t="s">
         <v>911</v>
       </c>
-      <c r="AA285" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="286" spans="10:29" s="28" customFormat="1" ht="15" customHeight="1">
-      <c r="J286" s="29" t="s">
+      <c r="P286" s="32" t="s">
+        <v>1307</v>
+      </c>
+      <c r="Q286" s="31" t="s">
         <v>912</v>
       </c>
-      <c r="O286" s="29" t="s">
+      <c r="R286" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="V286" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="W286" s="31"/>
+      <c r="Y286" s="31" t="s">
+        <v>911</v>
+      </c>
+      <c r="AA286" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB286" s="18" t="s">
         <v>913</v>
-      </c>
-      <c r="P286" s="30" t="s">
-        <v>914</v>
-      </c>
-      <c r="Q286" s="29" t="s">
-        <v>915</v>
-      </c>
-      <c r="R286" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="V286" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="W286" s="29"/>
-      <c r="Y286" s="29" t="s">
-        <v>913</v>
-      </c>
-      <c r="AA286" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB286" s="28" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="287" spans="10:29" ht="30" customHeight="1">
       <c r="J287" s="8" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="O287" s="8" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="P287" s="7" t="s">
         <v>364</v>
       </c>
       <c r="Q287" s="8" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="R287" s="8" t="s">
         <v>116</v>
@@ -12763,27 +12820,27 @@
       </c>
       <c r="W287" s="8"/>
       <c r="Y287" s="8" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="AA287" t="s">
         <v>54</v>
       </c>
       <c r="AC287" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="288" spans="10:29" ht="30" customHeight="1">
       <c r="J288" s="8" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="O288" s="8" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="P288" s="7" t="s">
-        <v>364</v>
+        <v>1308</v>
       </c>
       <c r="Q288" s="8" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="R288" s="8" t="s">
         <v>116</v>
@@ -12793,27 +12850,27 @@
       </c>
       <c r="W288" s="8"/>
       <c r="Y288" s="8" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="AA288" t="s">
         <v>38</v>
       </c>
       <c r="AB288" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="289" spans="10:28" ht="30" customHeight="1">
       <c r="J289" s="8" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="O289" s="8" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="P289" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q289" s="8" t="s">
-        <v>927</v>
+        <v>1309</v>
+      </c>
+      <c r="Q289" s="8">
+        <v>1</v>
       </c>
       <c r="R289" s="8" t="s">
         <v>36</v>
@@ -12823,24 +12880,24 @@
       </c>
       <c r="W289" s="8"/>
       <c r="Y289" s="8" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="AA289" t="s">
         <v>38</v>
       </c>
       <c r="AB289" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
     <row r="290" spans="10:28" ht="30" customHeight="1">
       <c r="J290" s="8" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="O290" s="8" t="s">
         <v>265</v>
       </c>
       <c r="P290" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q290" s="8">
         <v>20000101000000</v>
@@ -12853,7 +12910,7 @@
       </c>
       <c r="W290" s="8"/>
       <c r="Y290" s="8" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="AA290" t="s">
         <v>54</v>
@@ -12861,16 +12918,16 @@
     </row>
     <row r="291" spans="10:28" ht="30" customHeight="1">
       <c r="J291" s="8" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="O291" s="8" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="P291" s="7" t="s">
         <v>148</v>
       </c>
       <c r="Q291" s="8" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="R291" s="8" t="s">
         <v>71</v>
@@ -12879,10 +12936,10 @@
         <v>52</v>
       </c>
       <c r="W291" s="8" t="s">
-        <v>935</v>
+        <v>1310</v>
       </c>
       <c r="Y291" s="8" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="AA291" t="s">
         <v>38</v>
@@ -12893,16 +12950,16 @@
     </row>
     <row r="292" spans="10:28" ht="15" customHeight="1">
       <c r="J292" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="O292" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="O292" s="8" t="s">
-        <v>937</v>
-      </c>
       <c r="P292" s="7" t="s">
-        <v>148</v>
+        <v>1311</v>
       </c>
       <c r="Q292" s="8" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="R292" s="8" t="s">
         <v>116</v>
@@ -12912,27 +12969,27 @@
       </c>
       <c r="W292" s="8"/>
       <c r="Y292" s="8" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="AA292" t="s">
         <v>38</v>
       </c>
       <c r="AB292" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
     <row r="293" spans="10:28" ht="15" customHeight="1">
       <c r="J293" s="8" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="O293" s="8" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="P293" s="7" t="s">
-        <v>148</v>
+        <v>1311</v>
       </c>
       <c r="Q293" s="8" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="R293" s="8" t="s">
         <v>116</v>
@@ -12942,24 +12999,24 @@
       </c>
       <c r="W293" s="8"/>
       <c r="Y293" s="8" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="AA293" t="s">
         <v>38</v>
       </c>
       <c r="AB293" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="294" spans="10:28" ht="30" customHeight="1">
       <c r="J294" s="8" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="O294" s="8" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="P294" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q294" s="8">
         <v>20000101000000</v>
@@ -12972,7 +13029,7 @@
       </c>
       <c r="W294" s="8"/>
       <c r="Y294" s="8" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="AA294" t="s">
         <v>54</v>
@@ -12980,16 +13037,16 @@
     </row>
     <row r="295" spans="10:28" ht="15" customHeight="1">
       <c r="J295" s="8" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="O295" s="8" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="P295" s="7" t="s">
         <v>148</v>
       </c>
       <c r="Q295" s="8" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="R295" s="8" t="s">
         <v>36</v>
@@ -12999,7 +13056,7 @@
       </c>
       <c r="W295" s="8"/>
       <c r="Y295" s="8" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="AA295" t="s">
         <v>54</v>
@@ -13007,13 +13064,13 @@
     </row>
     <row r="296" spans="10:28" ht="30" customHeight="1">
       <c r="J296" s="8" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="O296" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="P296" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q296" s="8">
         <v>20000101000000</v>
@@ -13026,7 +13083,7 @@
       </c>
       <c r="W296" s="8"/>
       <c r="Y296" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="AA296" t="s">
         <v>54</v>
@@ -13034,28 +13091,28 @@
     </row>
     <row r="297" spans="10:28" ht="30" customHeight="1">
       <c r="J297" s="8" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="O297" s="8" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="P297" s="7" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="Q297" s="8" t="s">
         <v>50</v>
       </c>
       <c r="R297" s="8" t="s">
-        <v>71</v>
+        <v>1312</v>
       </c>
       <c r="V297" s="7" t="s">
         <v>52</v>
       </c>
       <c r="W297" s="8" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Y297" s="8" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="AA297" t="s">
         <v>38</v>
@@ -13066,16 +13123,16 @@
     </row>
     <row r="298" spans="10:28" ht="30" customHeight="1">
       <c r="J298" s="8" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="O298" s="8" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="P298" s="7" t="s">
         <v>144</v>
       </c>
       <c r="Q298" s="8" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="R298" s="8" t="s">
         <v>116</v>
@@ -13085,7 +13142,7 @@
       </c>
       <c r="W298" s="8"/>
       <c r="Y298" s="8" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="AA298" t="s">
         <v>54</v>
@@ -13093,16 +13150,16 @@
     </row>
     <row r="299" spans="10:28" ht="15" customHeight="1">
       <c r="J299" s="8" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="O299" s="8" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="P299" s="7" t="s">
-        <v>900</v>
+        <v>1313</v>
       </c>
       <c r="Q299" s="8" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="R299" s="8" t="s">
         <v>116</v>
@@ -13112,27 +13169,27 @@
       </c>
       <c r="W299" s="8"/>
       <c r="Y299" s="8" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="AA299" t="s">
         <v>38</v>
       </c>
       <c r="AB299" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
     </row>
     <row r="300" spans="10:28" ht="30" customHeight="1">
       <c r="J300" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="O300" s="8" t="s">
         <v>954</v>
-      </c>
-      <c r="O300" s="8" t="s">
-        <v>959</v>
       </c>
       <c r="P300" s="7" t="s">
         <v>45</v>
       </c>
       <c r="Q300" s="8" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="R300" s="8" t="s">
         <v>71</v>
@@ -13141,10 +13198,10 @@
         <v>52</v>
       </c>
       <c r="W300" s="8" t="s">
-        <v>961</v>
+        <v>1314</v>
       </c>
       <c r="Y300" s="8" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="AA300" t="s">
         <v>38</v>
@@ -13155,16 +13212,16 @@
     </row>
     <row r="301" spans="10:28" ht="15" customHeight="1">
       <c r="J301" s="8" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="O301" s="8" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="P301" s="7" t="s">
         <v>135</v>
       </c>
       <c r="Q301" s="8" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="R301" s="8" t="s">
         <v>36</v>
@@ -13174,7 +13231,7 @@
       </c>
       <c r="W301" s="8"/>
       <c r="Y301" s="8" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="AA301" t="s">
         <v>54</v>
@@ -13182,13 +13239,13 @@
     </row>
     <row r="302" spans="10:28" ht="15" customHeight="1">
       <c r="J302" s="8" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="O302" s="8" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="P302" s="7" t="s">
-        <v>135</v>
+        <v>1315</v>
       </c>
       <c r="Q302" s="8" t="s">
         <v>115</v>
@@ -13201,27 +13258,27 @@
       </c>
       <c r="W302" s="8"/>
       <c r="Y302" s="8" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="AA302" t="s">
         <v>38</v>
       </c>
       <c r="AB302" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
     </row>
     <row r="303" spans="10:28" ht="15" customHeight="1">
       <c r="J303" s="8" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="O303" s="8" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="P303" s="7" t="s">
         <v>135</v>
       </c>
       <c r="Q303" s="8" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="R303" s="8" t="s">
         <v>36</v>
@@ -13231,7 +13288,7 @@
       </c>
       <c r="W303" s="8"/>
       <c r="Y303" s="8" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="AA303" t="s">
         <v>54</v>
@@ -13239,16 +13296,16 @@
     </row>
     <row r="304" spans="10:28" ht="15" customHeight="1">
       <c r="J304" s="8" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="O304" s="8" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="P304" s="7" t="s">
         <v>135</v>
       </c>
       <c r="Q304" s="8" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="R304" s="8" t="s">
         <v>116</v>
@@ -13258,7 +13315,7 @@
       </c>
       <c r="W304" s="8"/>
       <c r="Y304" s="8" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="AA304" t="s">
         <v>54</v>
@@ -13266,13 +13323,13 @@
     </row>
     <row r="305" spans="10:29" ht="30" customHeight="1">
       <c r="J305" s="8" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="O305" s="8" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="P305" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q305" s="8">
         <v>20000101000000</v>
@@ -13285,7 +13342,7 @@
       </c>
       <c r="W305" s="8"/>
       <c r="Y305" s="8" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="AA305" t="s">
         <v>54</v>
@@ -13293,16 +13350,16 @@
     </row>
     <row r="306" spans="10:29" ht="30" customHeight="1">
       <c r="J306" s="8" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="O306" s="8" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="P306" s="7" t="s">
         <v>135</v>
       </c>
       <c r="Q306" s="23" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="R306" s="8" t="s">
         <v>76</v>
@@ -13312,7 +13369,7 @@
       </c>
       <c r="W306" s="8"/>
       <c r="Y306" s="8" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="AA306" t="s">
         <v>54</v>
@@ -13320,16 +13377,16 @@
     </row>
     <row r="307" spans="10:29" ht="30" customHeight="1">
       <c r="J307" s="8" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="O307" s="8" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="P307" s="7" t="s">
-        <v>148</v>
+        <v>1311</v>
       </c>
       <c r="Q307" s="8" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="R307" s="8" t="s">
         <v>116</v>
@@ -13339,27 +13396,27 @@
       </c>
       <c r="W307" s="8"/>
       <c r="Y307" s="8" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="AA307" t="s">
         <v>38</v>
       </c>
       <c r="AB307" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
     </row>
     <row r="308" spans="10:29" ht="30" customHeight="1">
       <c r="J308" s="8" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="O308" s="8" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="P308" s="7" t="s">
         <v>135</v>
       </c>
       <c r="Q308" s="8" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="R308" s="8" t="s">
         <v>36</v>
@@ -13369,24 +13426,24 @@
       </c>
       <c r="W308" s="8"/>
       <c r="Y308" s="8" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="AA308" t="s">
         <v>54</v>
       </c>
       <c r="AC308" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="309" spans="10:29" ht="30" customHeight="1">
       <c r="J309" s="8" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="O309" s="8" t="s">
         <v>170</v>
       </c>
       <c r="P309" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q309" s="8">
         <v>20000101000000</v>
@@ -13399,7 +13456,7 @@
       </c>
       <c r="W309" s="8"/>
       <c r="Y309" s="8" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="AA309" t="s">
         <v>54</v>
@@ -13407,16 +13464,16 @@
     </row>
     <row r="310" spans="10:29" ht="30" customHeight="1">
       <c r="J310" s="8" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="O310" s="8" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="P310" s="7" t="s">
         <v>135</v>
       </c>
       <c r="Q310" s="8" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="R310" s="8" t="s">
         <v>71</v>
@@ -13425,10 +13482,10 @@
         <v>52</v>
       </c>
       <c r="W310" s="8" t="s">
-        <v>992</v>
+        <v>1316</v>
       </c>
       <c r="Y310" s="8" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="AA310" t="s">
         <v>38</v>
@@ -13439,16 +13496,16 @@
     </row>
     <row r="311" spans="10:29" ht="15" customHeight="1">
       <c r="J311" s="8" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="O311" s="8" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="P311" s="7" t="s">
-        <v>135</v>
+        <v>1315</v>
       </c>
       <c r="Q311" s="8" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="R311" s="8" t="s">
         <v>116</v>
@@ -13458,27 +13515,27 @@
       </c>
       <c r="W311" s="8"/>
       <c r="Y311" s="8" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="AA311" t="s">
         <v>38</v>
       </c>
       <c r="AB311" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
     </row>
     <row r="312" spans="10:29" ht="15" customHeight="1">
       <c r="J312" s="8" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="O312" s="8" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="P312" s="7" t="s">
         <v>135</v>
       </c>
       <c r="Q312" s="8" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="R312" s="8" t="s">
         <v>36</v>
@@ -13488,27 +13545,27 @@
       </c>
       <c r="W312" s="8"/>
       <c r="Y312" s="8" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="AA312" t="s">
         <v>54</v>
       </c>
       <c r="AC312" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
     </row>
     <row r="313" spans="10:29" ht="15" customHeight="1">
       <c r="J313" s="8" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="O313" s="8" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="P313" s="7" t="s">
         <v>139</v>
       </c>
       <c r="Q313" s="8" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="R313" s="8" t="s">
         <v>36</v>
@@ -13518,7 +13575,7 @@
       </c>
       <c r="W313" s="8"/>
       <c r="Y313" s="8" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="AA313" t="s">
         <v>54</v>
@@ -13526,16 +13583,16 @@
     </row>
     <row r="314" spans="10:29" ht="15" customHeight="1">
       <c r="J314" s="8" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="O314" s="8" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="P314" s="7" t="s">
-        <v>183</v>
+        <v>1317</v>
       </c>
       <c r="Q314" s="8" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="R314" s="8" t="s">
         <v>116</v>
@@ -13545,27 +13602,27 @@
       </c>
       <c r="W314" s="8"/>
       <c r="Y314" s="8" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="AA314" t="s">
         <v>38</v>
       </c>
       <c r="AB314" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="315" spans="10:29" ht="15" customHeight="1">
       <c r="J315" s="8" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="O315" s="8" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="P315" s="7" t="s">
         <v>139</v>
       </c>
       <c r="Q315" s="8" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="R315" s="8" t="s">
         <v>116</v>
@@ -13575,27 +13632,27 @@
       </c>
       <c r="W315" s="8"/>
       <c r="Y315" s="8" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="AA315" t="s">
         <v>38</v>
       </c>
       <c r="AB315" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="316" spans="10:29" ht="30" customHeight="1">
       <c r="J316" s="8" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="O316" s="8" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="P316" s="7" t="s">
-        <v>781</v>
+        <v>1318</v>
       </c>
       <c r="Q316" s="8" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="R316" s="8" t="s">
         <v>116</v>
@@ -13605,27 +13662,27 @@
       </c>
       <c r="W316" s="8"/>
       <c r="Y316" s="8" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="AA316" t="s">
         <v>38</v>
       </c>
       <c r="AB316" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="317" spans="10:29" ht="15" customHeight="1">
       <c r="J317" s="8" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="O317" s="8" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="P317" s="7" t="s">
-        <v>781</v>
+        <v>1318</v>
       </c>
       <c r="Q317" s="8" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="R317" s="8" t="s">
         <v>116</v>
@@ -13635,27 +13692,27 @@
       </c>
       <c r="W317" s="8"/>
       <c r="Y317" s="8" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="AA317" t="s">
         <v>38</v>
       </c>
       <c r="AB317" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="318" spans="10:29" ht="30" customHeight="1">
       <c r="J318" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="O318" s="8" t="s">
         <v>1013</v>
-      </c>
-      <c r="O318" s="8" t="s">
-        <v>1020</v>
       </c>
       <c r="P318" s="7" t="s">
         <v>155</v>
       </c>
       <c r="Q318" s="8" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="R318" s="8" t="s">
         <v>116</v>
@@ -13665,7 +13722,7 @@
       </c>
       <c r="W318" s="8"/>
       <c r="Y318" s="8" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="AA318" t="s">
         <v>54</v>
@@ -13673,16 +13730,16 @@
     </row>
     <row r="319" spans="10:29" ht="15" customHeight="1">
       <c r="J319" s="8" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="O319" s="8" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="P319" s="7" t="s">
         <v>139</v>
       </c>
       <c r="Q319" s="8" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="R319" s="8" t="s">
         <v>116</v>
@@ -13692,27 +13749,27 @@
       </c>
       <c r="W319" s="8"/>
       <c r="Y319" s="8" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="AA319" t="s">
         <v>54</v>
       </c>
       <c r="AC319" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="320" spans="10:29" ht="30" customHeight="1">
       <c r="J320" s="8" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="O320" s="8" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="P320" s="7" t="s">
         <v>139</v>
       </c>
       <c r="Q320" s="8" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="R320" s="8" t="s">
         <v>116</v>
@@ -13722,27 +13779,27 @@
       </c>
       <c r="W320" s="8"/>
       <c r="Y320" s="8" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="AA320" t="s">
         <v>54</v>
       </c>
       <c r="AC320" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="321" spans="10:29" ht="15" customHeight="1">
       <c r="J321" s="8" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="O321" s="8" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="P321" s="7" t="s">
         <v>139</v>
       </c>
       <c r="Q321" s="8" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="R321" s="8" t="s">
         <v>116</v>
@@ -13752,27 +13809,27 @@
       </c>
       <c r="W321" s="8"/>
       <c r="Y321" s="8" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="AA321" t="s">
         <v>54</v>
       </c>
       <c r="AC321" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="322" spans="10:29" ht="15" customHeight="1">
       <c r="J322" s="8" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="O322" s="8" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="P322" s="7" t="s">
         <v>139</v>
       </c>
       <c r="Q322" s="8" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="R322" s="8" t="s">
         <v>116</v>
@@ -13782,18 +13839,18 @@
       </c>
       <c r="W322" s="8"/>
       <c r="Y322" s="8" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="AA322" t="s">
         <v>54</v>
       </c>
       <c r="AC322" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="323" spans="10:29" ht="15" customHeight="1">
       <c r="J323" s="8" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="O323" s="8" t="s">
         <v>326</v>
@@ -13812,7 +13869,7 @@
       </c>
       <c r="W323" s="8"/>
       <c r="Y323" s="8" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="AA323" t="s">
         <v>54</v>
@@ -13820,13 +13877,13 @@
     </row>
     <row r="324" spans="10:29" ht="105" customHeight="1">
       <c r="J324" s="8" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="O324" s="8" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="P324" s="7" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="Q324" s="8" t="s">
         <v>293</v>
@@ -13835,11 +13892,13 @@
         <v>51</v>
       </c>
       <c r="V324" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="W324" s="8"/>
+        <v>1319</v>
+      </c>
+      <c r="W324" s="8" t="s">
+        <v>1321</v>
+      </c>
       <c r="Y324" s="8" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="AA324" t="s">
         <v>38</v>
@@ -13850,13 +13909,13 @@
     </row>
     <row r="325" spans="10:29" ht="60" customHeight="1">
       <c r="J325" s="8" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="O325" s="8" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="P325" s="7" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="Q325" s="8" t="s">
         <v>56</v>
@@ -13867,9 +13926,11 @@
       <c r="V325" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="W325" s="8"/>
+      <c r="W325" s="8" t="s">
+        <v>1320</v>
+      </c>
       <c r="Y325" s="8" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="AA325" t="s">
         <v>38</v>
@@ -13880,13 +13941,13 @@
     </row>
     <row r="326" spans="10:29" ht="15" customHeight="1">
       <c r="J326" s="8" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="O326" s="8" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="P326" s="7" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="Q326" s="8" t="s">
         <v>52</v>
@@ -13898,10 +13959,10 @@
         <v>52</v>
       </c>
       <c r="W326" s="8" t="s">
-        <v>598</v>
+        <v>1322</v>
       </c>
       <c r="Y326" s="8" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="AA326" t="s">
         <v>38</v>
@@ -13912,10 +13973,10 @@
     </row>
     <row r="327" spans="10:29" ht="45" customHeight="1">
       <c r="J327" s="8" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="O327" s="8" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="P327" s="7" t="s">
         <v>45</v>
@@ -13931,27 +13992,27 @@
       </c>
       <c r="W327" s="8"/>
       <c r="Y327" s="8" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="AA327" t="s">
         <v>54</v>
       </c>
       <c r="AC327" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="328" spans="10:29" ht="15" customHeight="1">
       <c r="J328" s="8" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="O328" s="8" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="P328" s="7" t="s">
         <v>364</v>
       </c>
       <c r="Q328" s="8" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="R328" s="8" t="s">
         <v>36</v>
@@ -13961,21 +14022,21 @@
       </c>
       <c r="W328" s="8"/>
       <c r="Y328" s="8" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="AA328" t="s">
         <v>54</v>
       </c>
       <c r="AC328" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="329" spans="10:29" ht="45" customHeight="1">
       <c r="J329" s="8" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="O329" s="8" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="P329" s="7" t="s">
         <v>114</v>
@@ -13991,21 +14052,21 @@
       </c>
       <c r="W329" s="8"/>
       <c r="Y329" s="8" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="AA329" t="s">
         <v>54</v>
       </c>
       <c r="AC329" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="330" spans="10:29" ht="30" customHeight="1">
       <c r="J330" s="8" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="O330" s="8" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="P330" s="7" t="s">
         <v>114</v>
@@ -14021,27 +14082,27 @@
       </c>
       <c r="W330" s="8"/>
       <c r="Y330" s="8" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="AA330" t="s">
         <v>54</v>
       </c>
       <c r="AC330" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="331" spans="10:29" ht="45" customHeight="1">
       <c r="J331" s="8" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="O331" s="8" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="P331" s="7" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="Q331" s="8" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="R331" s="8" t="s">
         <v>36</v>
@@ -14051,27 +14112,27 @@
       </c>
       <c r="W331" s="8"/>
       <c r="Y331" s="8" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="AA331" t="s">
         <v>54</v>
       </c>
       <c r="AC331" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="332" spans="10:29" ht="15" customHeight="1">
       <c r="J332" s="8" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="O332" s="8" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="P332" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="Q332" s="8" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="R332" s="8" t="s">
         <v>36</v>
@@ -14081,7 +14142,7 @@
       </c>
       <c r="W332" s="8"/>
       <c r="Y332" s="8" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="AA332" t="s">
         <v>54</v>
@@ -14089,46 +14150,46 @@
     </row>
     <row r="333" spans="10:29" ht="15" customHeight="1">
       <c r="J333" s="8" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="O333" s="8" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="P333" s="7" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="Q333" s="8" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="R333" s="8" t="s">
-        <v>36</v>
+        <v>1323</v>
       </c>
       <c r="V333" s="7" t="s">
         <v>37</v>
       </c>
       <c r="W333" s="8"/>
       <c r="Y333" s="8" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="AA333" t="s">
         <v>38</v>
       </c>
       <c r="AB333" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="334" spans="10:29" ht="30" customHeight="1">
       <c r="J334" s="8" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="O334" s="8" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="P334" s="7" t="s">
         <v>183</v>
       </c>
       <c r="Q334" s="8" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="R334" s="8" t="s">
         <v>36</v>
@@ -14138,7 +14199,7 @@
       </c>
       <c r="W334" s="8"/>
       <c r="Y334" s="8" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="AA334" t="s">
         <v>54</v>
@@ -14146,10 +14207,10 @@
     </row>
     <row r="335" spans="10:29" ht="30" customHeight="1">
       <c r="J335" s="8" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="O335" s="8" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="P335" s="7" t="s">
         <v>42</v>
@@ -14165,7 +14226,7 @@
       </c>
       <c r="W335" s="8"/>
       <c r="Y335" s="8" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="AA335" t="s">
         <v>54</v>
@@ -14173,16 +14234,16 @@
     </row>
     <row r="336" spans="10:29" ht="30" customHeight="1">
       <c r="J336" s="8" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="O336" s="8" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="P336" s="7" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="Q336" s="8" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="R336" s="8" t="s">
         <v>71</v>
@@ -14191,10 +14252,10 @@
         <v>52</v>
       </c>
       <c r="W336" s="8" t="s">
-        <v>1087</v>
+        <v>1324</v>
       </c>
       <c r="Y336" s="8" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="AA336" t="s">
         <v>38</v>
@@ -14205,16 +14266,16 @@
     </row>
     <row r="337" spans="10:29" ht="45" customHeight="1">
       <c r="J337" s="8" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="O337" s="8" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="P337" s="7" t="s">
         <v>493</v>
       </c>
       <c r="Q337" s="8" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="R337" s="8" t="s">
         <v>65</v>
@@ -14224,7 +14285,7 @@
       </c>
       <c r="W337" s="8"/>
       <c r="Y337" s="8" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="AA337" t="s">
         <v>54</v>
@@ -14232,10 +14293,10 @@
     </row>
     <row r="338" spans="10:29" ht="45" customHeight="1">
       <c r="J338" s="8" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="O338" s="8" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="P338" s="7" t="s">
         <v>380</v>
@@ -14251,7 +14312,7 @@
       </c>
       <c r="W338" s="8"/>
       <c r="Y338" s="8" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="AA338" t="s">
         <v>54</v>
@@ -14259,16 +14320,16 @@
     </row>
     <row r="339" spans="10:29" ht="30" customHeight="1">
       <c r="J339" s="8" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="O339" s="8" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="P339" s="7" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="Q339" s="8" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
       <c r="R339" s="8" t="s">
         <v>65</v>
@@ -14278,7 +14339,7 @@
       </c>
       <c r="W339" s="8"/>
       <c r="Y339" s="8" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
       <c r="AA339" t="s">
         <v>54</v>
@@ -14286,16 +14347,16 @@
     </row>
     <row r="340" spans="10:29" ht="30" customHeight="1">
       <c r="J340" s="8" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="O340" s="8" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="P340" s="7" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="Q340" s="8" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
       <c r="R340" s="8" t="s">
         <v>65</v>
@@ -14305,54 +14366,54 @@
       </c>
       <c r="W340" s="8"/>
       <c r="Y340" s="8" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
       <c r="AA340" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="341" spans="10:29" ht="15" customHeight="1">
-      <c r="J341" s="8" t="s">
-        <v>1101</v>
-      </c>
-      <c r="O341" s="8" t="s">
-        <v>1102</v>
-      </c>
-      <c r="P341" s="7" t="s">
+    <row r="341" spans="10:29" s="25" customFormat="1" ht="15" customHeight="1">
+      <c r="J341" s="26" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O341" s="26" t="s">
+        <v>1095</v>
+      </c>
+      <c r="P341" s="27" t="s">
         <v>470</v>
       </c>
-      <c r="Q341" s="8" t="s">
-        <v>1103</v>
-      </c>
-      <c r="R341" s="8" t="s">
+      <c r="Q341" s="26" t="s">
+        <v>1096</v>
+      </c>
+      <c r="R341" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="V341" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="W341" s="8"/>
-      <c r="Y341" s="8" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AA341" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC341" t="s">
-        <v>1104</v>
+      <c r="V341" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="W341" s="26"/>
+      <c r="Y341" s="26" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AA341" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC341" s="25" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="342" spans="10:29" ht="15" customHeight="1">
       <c r="J342" s="8" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
       <c r="O342" s="8" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="P342" s="7" t="s">
         <v>470</v>
       </c>
       <c r="Q342" s="8" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="R342" s="8" t="s">
         <v>116</v>
@@ -14362,27 +14423,27 @@
       </c>
       <c r="W342" s="8"/>
       <c r="Y342" s="8" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="AA342" t="s">
         <v>54</v>
       </c>
       <c r="AC342" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="343" spans="10:29" ht="15" customHeight="1">
       <c r="J343" s="8" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O343" s="8" t="s">
         <v>1101</v>
-      </c>
-      <c r="O343" s="8" t="s">
-        <v>1108</v>
       </c>
       <c r="P343" s="7" t="s">
         <v>470</v>
       </c>
       <c r="Q343" s="8" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="R343" s="8" t="s">
         <v>116</v>
@@ -14392,27 +14453,27 @@
       </c>
       <c r="W343" s="8"/>
       <c r="Y343" s="8" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="AA343" t="s">
         <v>54</v>
       </c>
       <c r="AC343" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="344" spans="10:29" ht="45" customHeight="1">
       <c r="J344" s="8" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
       <c r="O344" s="8" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="P344" s="7" t="s">
         <v>470</v>
       </c>
       <c r="Q344" s="8" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="R344" s="8" t="s">
         <v>116</v>
@@ -14422,27 +14483,27 @@
       </c>
       <c r="W344" s="8"/>
       <c r="Y344" s="8" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="AA344" t="s">
         <v>38</v>
       </c>
       <c r="AB344" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="345" spans="10:29" ht="30" customHeight="1">
       <c r="J345" s="8" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
       <c r="O345" s="8" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="P345" s="7" t="s">
         <v>144</v>
       </c>
       <c r="Q345" s="8" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="R345" s="8" t="s">
         <v>116</v>
@@ -14452,24 +14513,24 @@
       </c>
       <c r="W345" s="8"/>
       <c r="Y345" s="8" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
       <c r="AA345" t="s">
         <v>54</v>
       </c>
       <c r="AC345" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="346" spans="10:29" ht="15" customHeight="1">
       <c r="J346" s="13" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="O346" s="13" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="P346" s="14" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
       <c r="Q346" s="13" t="s">
         <v>494</v>
@@ -14481,27 +14542,27 @@
         <v>37</v>
       </c>
       <c r="Y346" s="13" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="AA346" t="s">
         <v>38</v>
       </c>
       <c r="AB346" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="347" spans="10:29" ht="15" customHeight="1">
       <c r="J347" s="13" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="O347" s="13" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="P347" s="14" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Q347" s="13" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="R347" s="13" t="s">
         <v>36</v>
@@ -14510,7 +14571,7 @@
         <v>37</v>
       </c>
       <c r="Y347" s="13" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="AA347" t="s">
         <v>54</v>
@@ -14518,16 +14579,16 @@
     </row>
     <row r="348" spans="10:29" ht="15" customHeight="1">
       <c r="J348" s="13" t="s">
+        <v>1112</v>
+      </c>
+      <c r="O348" s="13" t="s">
         <v>1119</v>
       </c>
-      <c r="O348" s="13" t="s">
-        <v>1126</v>
-      </c>
       <c r="P348" s="14" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
       <c r="Q348" s="13" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="R348" s="13" t="s">
         <v>116</v>
@@ -14536,27 +14597,27 @@
         <v>37</v>
       </c>
       <c r="Y348" s="13" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="AA348" t="s">
         <v>38</v>
       </c>
       <c r="AB348" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="349" spans="10:29" ht="15" customHeight="1">
       <c r="J349" s="13" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="O349" s="13" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
       <c r="P349" s="14" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="Q349" s="13" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="R349" s="13" t="s">
         <v>36</v>
@@ -14565,18 +14626,18 @@
         <v>37</v>
       </c>
       <c r="Y349" s="13" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="AA349" t="s">
         <v>54</v>
       </c>
       <c r="AC349" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="350" spans="10:29" ht="15" customHeight="1">
       <c r="J350" s="13" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="O350" s="13" t="s">
         <v>261</v>
@@ -14594,7 +14655,7 @@
         <v>37</v>
       </c>
       <c r="Y350" s="13" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="AA350" t="s">
         <v>54</v>
@@ -14602,10 +14663,10 @@
     </row>
     <row r="351" spans="10:29" ht="15" customHeight="1">
       <c r="J351" s="13" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="O351" s="13" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="P351" s="14" t="s">
         <v>42</v>
@@ -14620,7 +14681,7 @@
         <v>37</v>
       </c>
       <c r="Y351" s="13" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="AA351" t="s">
         <v>54</v>
@@ -14628,13 +14689,13 @@
     </row>
     <row r="352" spans="10:29" ht="15" customHeight="1">
       <c r="J352" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O352" s="13" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="P352" s="14" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Q352" s="13" t="s">
         <v>89</v>
@@ -14646,7 +14707,7 @@
         <v>37</v>
       </c>
       <c r="Y352" s="13" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="AA352" t="s">
         <v>54</v>
@@ -14654,20 +14715,20 @@
     </row>
     <row r="353" spans="10:29" ht="30" customHeight="1">
       <c r="J353" s="8" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="K353" s="15"/>
       <c r="L353" s="15"/>
       <c r="M353" s="15"/>
       <c r="N353" s="15"/>
       <c r="O353" s="8" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="P353" s="7" t="s">
         <v>308</v>
       </c>
       <c r="Q353" s="8" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="R353" s="8" t="s">
         <v>116</v>
@@ -14681,7 +14742,7 @@
       <c r="W353" s="15"/>
       <c r="X353" s="15"/>
       <c r="Y353" s="8" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="AA353" t="s">
         <v>54</v>
@@ -14689,10 +14750,10 @@
     </row>
     <row r="354" spans="10:29" ht="15" customHeight="1">
       <c r="J354" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O354" s="13" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="P354" s="14" t="s">
         <v>139</v>
@@ -14707,27 +14768,27 @@
         <v>37</v>
       </c>
       <c r="Y354" s="13" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="AA354" t="s">
         <v>54</v>
       </c>
       <c r="AC354" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="355" spans="10:29" ht="30" customHeight="1">
       <c r="J355" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O355" s="13" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="P355" s="14" t="s">
         <v>308</v>
       </c>
       <c r="Q355" s="13" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="R355" s="13" t="s">
         <v>116</v>
@@ -14736,7 +14797,7 @@
         <v>37</v>
       </c>
       <c r="Y355" s="13" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="AA355" t="s">
         <v>54</v>
@@ -14744,16 +14805,16 @@
     </row>
     <row r="356" spans="10:29" ht="30" customHeight="1">
       <c r="J356" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O356" s="13" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="P356" s="14" t="s">
         <v>308</v>
       </c>
       <c r="Q356" s="13" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="R356" s="13" t="s">
         <v>116</v>
@@ -14762,7 +14823,7 @@
         <v>37</v>
       </c>
       <c r="Y356" s="13" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="AA356" t="s">
         <v>54</v>
@@ -14770,16 +14831,16 @@
     </row>
     <row r="357" spans="10:29" ht="30" customHeight="1">
       <c r="J357" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O357" s="13" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="P357" s="14" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="Q357" s="13" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="R357" s="13" t="s">
         <v>116</v>
@@ -14788,7 +14849,7 @@
         <v>37</v>
       </c>
       <c r="Y357" s="13" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="AA357" t="s">
         <v>54</v>
@@ -14796,7 +14857,7 @@
     </row>
     <row r="358" spans="10:29" ht="15" customHeight="1">
       <c r="J358" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O358" s="13" t="s">
         <v>138</v>
@@ -14805,7 +14866,7 @@
         <v>470</v>
       </c>
       <c r="Q358" s="13" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
       <c r="R358" s="13" t="s">
         <v>36</v>
@@ -14814,27 +14875,27 @@
         <v>37</v>
       </c>
       <c r="Y358" s="13" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
       <c r="AA358" t="s">
         <v>54</v>
       </c>
       <c r="AC358" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="359" spans="10:29" ht="15" customHeight="1">
       <c r="J359" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O359" s="13" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P359" s="14" t="s">
         <v>470</v>
       </c>
       <c r="Q359" s="13" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
       <c r="R359" s="13" t="s">
         <v>116</v>
@@ -14843,7 +14904,7 @@
         <v>37</v>
       </c>
       <c r="Y359" s="13" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="AA359" t="s">
         <v>54</v>
@@ -14851,16 +14912,16 @@
     </row>
     <row r="360" spans="10:29" ht="15" customHeight="1">
       <c r="J360" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O360" s="13" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
       <c r="P360" s="14" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Q360" s="13" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="R360" s="13" t="s">
         <v>116</v>
@@ -14869,27 +14930,27 @@
         <v>37</v>
       </c>
       <c r="Y360" s="13" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
       <c r="AA360" t="s">
         <v>54</v>
       </c>
       <c r="AC360" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="361" spans="10:29" ht="15" customHeight="1">
       <c r="J361" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O361" s="13" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
       <c r="P361" s="14" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Q361" s="13" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
       <c r="R361" s="13" t="s">
         <v>116</v>
@@ -14898,21 +14959,21 @@
         <v>37</v>
       </c>
       <c r="Y361" s="13" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="AA361" t="s">
         <v>54</v>
       </c>
       <c r="AC361" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="362" spans="10:29" ht="15" customHeight="1">
       <c r="J362" s="13" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="O362" s="13" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
       <c r="P362" s="14" t="s">
         <v>49</v>
@@ -14927,7 +14988,7 @@
         <v>37</v>
       </c>
       <c r="Y362" s="13" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="AA362" t="s">
         <v>38</v>
@@ -14938,16 +14999,16 @@
     </row>
     <row r="363" spans="10:29" ht="15" customHeight="1">
       <c r="J363" s="13" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="O363" s="13" t="s">
-        <v>1169</v>
+        <v>1162</v>
       </c>
       <c r="P363" s="14" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Q363" s="13" t="s">
-        <v>1170</v>
+        <v>1163</v>
       </c>
       <c r="R363" s="13" t="s">
         <v>116</v>
@@ -14956,7 +15017,7 @@
         <v>37</v>
       </c>
       <c r="Y363" s="13" t="s">
-        <v>1171</v>
+        <v>1164</v>
       </c>
       <c r="AA363" t="s">
         <v>54</v>
@@ -14964,16 +15025,16 @@
     </row>
     <row r="364" spans="10:29" ht="30" customHeight="1">
       <c r="J364" s="13" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="O364" s="13" t="s">
-        <v>1172</v>
+        <v>1165</v>
       </c>
       <c r="P364" s="14" t="s">
         <v>155</v>
       </c>
       <c r="Q364" s="13" t="s">
-        <v>1173</v>
+        <v>1166</v>
       </c>
       <c r="R364" s="13" t="s">
         <v>116</v>
@@ -14982,7 +15043,7 @@
         <v>37</v>
       </c>
       <c r="Y364" s="13" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
       <c r="AA364" t="s">
         <v>54</v>
@@ -14990,16 +15051,16 @@
     </row>
     <row r="365" spans="10:29" ht="15" customHeight="1">
       <c r="J365" s="13" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
       <c r="O365" s="13" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
       <c r="P365" s="14" t="s">
         <v>470</v>
       </c>
       <c r="Q365" s="13" t="s">
-        <v>1177</v>
+        <v>1170</v>
       </c>
       <c r="R365" s="13" t="s">
         <v>36</v>
@@ -15008,7 +15069,7 @@
         <v>37</v>
       </c>
       <c r="Y365" s="13" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
       <c r="AA365" t="s">
         <v>54</v>
@@ -15016,7 +15077,7 @@
     </row>
     <row r="366" spans="10:29" ht="15" customHeight="1">
       <c r="J366" s="13" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
       <c r="O366" s="13" t="s">
         <v>261</v>
@@ -15034,7 +15095,7 @@
         <v>37</v>
       </c>
       <c r="Y366" s="13" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="AA366" t="s">
         <v>54</v>
@@ -15042,16 +15103,16 @@
     </row>
     <row r="367" spans="10:29" ht="30" customHeight="1">
       <c r="J367" s="13" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="O367" s="13" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="P367" s="14" t="s">
         <v>470</v>
       </c>
       <c r="Q367" s="13" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="R367" s="13" t="s">
         <v>36</v>
@@ -15060,7 +15121,7 @@
         <v>37</v>
       </c>
       <c r="Y367" s="13" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="AA367" t="s">
         <v>54</v>
@@ -15068,16 +15129,16 @@
     </row>
     <row r="368" spans="10:29" ht="30" customHeight="1">
       <c r="J368" s="13" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="O368" s="13" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="P368" s="14" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="Q368" s="13" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="R368" s="13" t="s">
         <v>116</v>
@@ -15086,7 +15147,7 @@
         <v>37</v>
       </c>
       <c r="Y368" s="13" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="AA368" t="s">
         <v>54</v>
@@ -15094,16 +15155,16 @@
     </row>
     <row r="369" spans="10:29" ht="30" customHeight="1">
       <c r="J369" s="13" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="O369" s="13" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
       <c r="P369" s="14" t="s">
         <v>114</v>
       </c>
       <c r="Q369" s="13" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="R369" s="13" t="s">
         <v>116</v>
@@ -15112,27 +15173,27 @@
         <v>37</v>
       </c>
       <c r="Y369" s="13" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
       <c r="AA369" t="s">
         <v>38</v>
       </c>
       <c r="AB369" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="370" spans="10:29" ht="30" customHeight="1">
       <c r="J370" s="13" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="O370" s="13" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="P370" s="14" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="Q370" s="13" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="R370" s="13" t="s">
         <v>116</v>
@@ -15141,7 +15202,7 @@
         <v>37</v>
       </c>
       <c r="Y370" s="13" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="AA370" t="s">
         <v>54</v>
@@ -15149,16 +15210,16 @@
     </row>
     <row r="371" spans="10:29" ht="30" customHeight="1">
       <c r="J371" s="13" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O371" s="13" t="s">
+        <v>1190</v>
+      </c>
+      <c r="P371" s="14" t="s">
+        <v>1191</v>
+      </c>
+      <c r="Q371" s="13" t="s">
         <v>1192</v>
-      </c>
-      <c r="O371" s="13" t="s">
-        <v>1197</v>
-      </c>
-      <c r="P371" s="14" t="s">
-        <v>1198</v>
-      </c>
-      <c r="Q371" s="13" t="s">
-        <v>1199</v>
       </c>
       <c r="R371" s="13" t="s">
         <v>116</v>
@@ -15167,27 +15228,27 @@
         <v>37</v>
       </c>
       <c r="Y371" s="13" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
       <c r="AA371" t="s">
         <v>54</v>
       </c>
       <c r="AC371" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="372" spans="10:29" ht="30" customHeight="1">
       <c r="J372" s="8" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="O372" s="8" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
       <c r="P372" s="7" t="s">
         <v>470</v>
       </c>
       <c r="Q372" s="8" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
       <c r="R372" s="8" t="s">
         <v>36</v>
@@ -15196,7 +15257,7 @@
         <v>37</v>
       </c>
       <c r="Y372" s="8" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="AA372" t="s">
         <v>54</v>
@@ -15204,16 +15265,16 @@
     </row>
     <row r="373" spans="10:29" ht="30" customHeight="1">
       <c r="J373" s="8" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="O373" s="8" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
       <c r="P373" s="7" t="s">
         <v>155</v>
       </c>
       <c r="Q373" s="8" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="R373" s="8" t="s">
         <v>116</v>
@@ -15222,7 +15283,7 @@
         <v>37</v>
       </c>
       <c r="Y373" s="8" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="AA373" t="s">
         <v>54</v>
@@ -15230,10 +15291,10 @@
     </row>
     <row r="374" spans="10:29" ht="30" customHeight="1">
       <c r="J374" s="8" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="O374" s="8" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="P374" s="7" t="s">
         <v>49</v>
@@ -15248,7 +15309,7 @@
         <v>37</v>
       </c>
       <c r="Y374" s="8" t="s">
-        <v>1210</v>
+        <v>1203</v>
       </c>
       <c r="AA374" t="s">
         <v>38</v>
@@ -15259,10 +15320,10 @@
     </row>
     <row r="375" spans="10:29" ht="30" customHeight="1">
       <c r="J375" s="8" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="O375" s="8" t="s">
-        <v>1211</v>
+        <v>1204</v>
       </c>
       <c r="P375" s="7" t="s">
         <v>49</v>
@@ -15277,7 +15338,7 @@
         <v>37</v>
       </c>
       <c r="Y375" s="8" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="AA375" t="s">
         <v>38</v>
@@ -15288,10 +15349,10 @@
     </row>
     <row r="376" spans="10:29" ht="30" customHeight="1">
       <c r="J376" s="8" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="O376" s="8" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="P376" s="7" t="s">
         <v>49</v>
@@ -15306,7 +15367,7 @@
         <v>37</v>
       </c>
       <c r="Y376" s="8" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="AA376" t="s">
         <v>38</v>
@@ -15317,10 +15378,10 @@
     </row>
     <row r="377" spans="10:29" ht="30" customHeight="1">
       <c r="J377" s="8" t="s">
+        <v>1201</v>
+      </c>
+      <c r="O377" s="8" t="s">
         <v>1208</v>
-      </c>
-      <c r="O377" s="8" t="s">
-        <v>1215</v>
       </c>
       <c r="P377" s="7" t="s">
         <v>49</v>
@@ -15335,7 +15396,7 @@
         <v>37</v>
       </c>
       <c r="Y377" s="8" t="s">
-        <v>1216</v>
+        <v>1209</v>
       </c>
       <c r="AA377" t="s">
         <v>38</v>
@@ -15346,16 +15407,16 @@
     </row>
     <row r="378" spans="10:29" ht="30" customHeight="1">
       <c r="J378" s="8" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="O378" s="8" t="s">
-        <v>1217</v>
+        <v>1210</v>
       </c>
       <c r="P378" s="7" t="s">
-        <v>1218</v>
+        <v>1211</v>
       </c>
       <c r="Q378" s="8" t="s">
-        <v>1219</v>
+        <v>1212</v>
       </c>
       <c r="R378" s="8" t="s">
         <v>116</v>
@@ -15364,27 +15425,27 @@
         <v>37</v>
       </c>
       <c r="Y378" s="8" t="s">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="AA378" t="s">
         <v>38</v>
       </c>
       <c r="AB378" t="s">
-        <v>1221</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="379" spans="10:29">
       <c r="J379" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O379" s="20" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
       <c r="P379" s="20" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="Q379" s="21" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
       <c r="R379" s="20" t="s">
         <v>36</v>
@@ -15394,7 +15455,7 @@
       </c>
       <c r="W379" s="20"/>
       <c r="Y379" s="20" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
       <c r="AA379" t="s">
         <v>54</v>
@@ -15402,16 +15463,16 @@
     </row>
     <row r="380" spans="10:29">
       <c r="J380" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O380" s="20" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
       <c r="P380" s="20" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="Q380" s="21" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
       <c r="R380" s="20" t="s">
         <v>36</v>
@@ -15421,21 +15482,21 @@
       </c>
       <c r="W380" s="20"/>
       <c r="Y380" s="20" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
       <c r="AA380" t="s">
         <v>38</v>
       </c>
       <c r="AB380" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="381" spans="10:29">
       <c r="J381" s="20" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O381" s="20" t="s">
         <v>1222</v>
-      </c>
-      <c r="O381" s="20" t="s">
-        <v>1229</v>
       </c>
       <c r="P381" s="20" t="s">
         <v>139</v>
@@ -15450,7 +15511,7 @@
         <v>52</v>
       </c>
       <c r="W381" s="20" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="Y381" s="20" t="s">
         <v>138</v>
@@ -15464,16 +15525,16 @@
     </row>
     <row r="382" spans="10:29">
       <c r="J382" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O382" s="20" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="P382" s="20" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="Q382" s="21" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
       <c r="R382" s="20" t="s">
         <v>36</v>
@@ -15483,27 +15544,27 @@
       </c>
       <c r="W382" s="20"/>
       <c r="Y382" s="20" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="AA382" t="s">
         <v>38</v>
       </c>
       <c r="AB382" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="383" spans="10:29">
       <c r="J383" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O383" s="20" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
       <c r="P383" s="20" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="Q383" s="21" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="R383" s="20" t="s">
         <v>36</v>
@@ -15513,7 +15574,7 @@
       </c>
       <c r="W383" s="20"/>
       <c r="Y383" s="20" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
       <c r="AA383" t="s">
         <v>54</v>
@@ -15521,16 +15582,16 @@
     </row>
     <row r="384" spans="10:29">
       <c r="J384" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O384" s="20" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="P384" s="20" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="Q384" s="21" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="R384" s="20" t="s">
         <v>116</v>
@@ -15540,21 +15601,21 @@
       </c>
       <c r="W384" s="20"/>
       <c r="Y384" s="20" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="AA384" t="s">
         <v>38</v>
       </c>
       <c r="AB384" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="385" spans="10:28">
       <c r="J385" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O385" s="20" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
       <c r="P385" s="20" t="s">
         <v>148</v>
@@ -15570,7 +15631,7 @@
       </c>
       <c r="W385" s="20"/>
       <c r="Y385" s="20" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
       <c r="AA385" t="s">
         <v>54</v>
@@ -15578,16 +15639,16 @@
     </row>
     <row r="386" spans="10:28">
       <c r="J386" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O386" s="20" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="P386" s="20" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="Q386" s="21" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
       <c r="R386" s="20" t="s">
         <v>36</v>
@@ -15597,27 +15658,27 @@
       </c>
       <c r="W386" s="20"/>
       <c r="Y386" s="20" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="AA386" t="s">
         <v>38</v>
       </c>
       <c r="AB386" t="s">
-        <v>1244</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="387" spans="10:28">
       <c r="J387" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O387" s="20" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="P387" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="Q387" s="21" t="s">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="R387" s="20" t="s">
         <v>71</v>
@@ -15626,10 +15687,10 @@
         <v>52</v>
       </c>
       <c r="W387" s="20" t="s">
-        <v>1247</v>
+        <v>1240</v>
       </c>
       <c r="Y387" s="20" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="AA387" t="s">
         <v>54</v>
@@ -15637,16 +15698,16 @@
     </row>
     <row r="388" spans="10:28">
       <c r="J388" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O388" s="20" t="s">
-        <v>1248</v>
+        <v>1241</v>
       </c>
       <c r="P388" s="20" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q388" s="21" t="s">
-        <v>1249</v>
+        <v>1242</v>
       </c>
       <c r="R388" s="20" t="s">
         <v>36</v>
@@ -15656,7 +15717,7 @@
       </c>
       <c r="W388" s="20"/>
       <c r="Y388" s="20" t="s">
-        <v>1248</v>
+        <v>1241</v>
       </c>
       <c r="AA388" t="s">
         <v>54</v>
@@ -15664,16 +15725,16 @@
     </row>
     <row r="389" spans="10:28">
       <c r="J389" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O389" s="20" t="s">
-        <v>1250</v>
+        <v>1243</v>
       </c>
       <c r="P389" s="20" t="s">
-        <v>1251</v>
+        <v>1244</v>
       </c>
       <c r="Q389" s="21" t="s">
-        <v>1252</v>
+        <v>1245</v>
       </c>
       <c r="R389" s="20" t="s">
         <v>116</v>
@@ -15683,27 +15744,27 @@
       </c>
       <c r="W389" s="20"/>
       <c r="Y389" s="20" t="s">
-        <v>1250</v>
+        <v>1243</v>
       </c>
       <c r="AA389" t="s">
         <v>38</v>
       </c>
       <c r="AB389" t="s">
-        <v>1253</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="390" spans="10:28">
       <c r="J390" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O390" s="20" t="s">
-        <v>1254</v>
+        <v>1247</v>
       </c>
       <c r="P390" s="20" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="Q390" s="21" t="s">
-        <v>1255</v>
+        <v>1248</v>
       </c>
       <c r="R390" s="20" t="s">
         <v>116</v>
@@ -15713,27 +15774,27 @@
       </c>
       <c r="W390" s="20"/>
       <c r="Y390" s="20" t="s">
-        <v>1254</v>
+        <v>1247</v>
       </c>
       <c r="AA390" t="s">
         <v>38</v>
       </c>
       <c r="AB390" t="s">
-        <v>1256</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="391" spans="10:28">
       <c r="J391" s="20" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="O391" s="20" t="s">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="P391" s="20" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="Q391" s="21" t="s">
-        <v>1255</v>
+        <v>1248</v>
       </c>
       <c r="R391" s="20" t="s">
         <v>116</v>
@@ -15743,13 +15804,13 @@
       </c>
       <c r="W391" s="20"/>
       <c r="Y391" s="20" t="s">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="AA391" t="s">
         <v>38</v>
       </c>
       <c r="AB391" t="s">
-        <v>1256</v>
+        <v>1249</v>
       </c>
     </row>
   </sheetData>
